--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -2101,10 +2101,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118668303</v>
+        <v>118668294</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2113,38 +2113,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474498</v>
+        <v>474399</v>
       </c>
       <c r="R14" t="n">
-        <v>6849066</v>
+        <v>6849297</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2179,12 +2187,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2313,10 +2327,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118668294</v>
+        <v>118668303</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2325,46 +2339,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474399</v>
+        <v>474498</v>
       </c>
       <c r="R16" t="n">
-        <v>6849297</v>
+        <v>6849066</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2399,18 +2405,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -3803,10 +3803,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118668282</v>
+        <v>118668265</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>79073</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3815,46 +3815,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474482</v>
+        <v>474281</v>
       </c>
       <c r="R29" t="n">
-        <v>6849109</v>
+        <v>6849316</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3889,18 +3881,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3923,10 +3909,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118668265</v>
+        <v>118668282</v>
       </c>
       <c r="B30" t="n">
-        <v>79073</v>
+        <v>97846</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3935,38 +3921,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474281</v>
+        <v>474482</v>
       </c>
       <c r="R30" t="n">
-        <v>6849316</v>
+        <v>6849109</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4001,12 +3995,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -3471,10 +3471,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118668305</v>
+        <v>118668279</v>
       </c>
       <c r="B26" t="n">
-        <v>78129</v>
+        <v>97846</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3483,38 +3483,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474253</v>
+        <v>474461</v>
       </c>
       <c r="R26" t="n">
-        <v>6849332</v>
+        <v>6849116</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3549,12 +3557,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3577,10 +3591,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118668279</v>
+        <v>118668305</v>
       </c>
       <c r="B27" t="n">
-        <v>97846</v>
+        <v>78129</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3589,46 +3603,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474461</v>
+        <v>474253</v>
       </c>
       <c r="R27" t="n">
-        <v>6849116</v>
+        <v>6849332</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3663,18 +3669,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3803,10 +3803,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118668265</v>
+        <v>118668282</v>
       </c>
       <c r="B29" t="n">
-        <v>79073</v>
+        <v>97846</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3815,38 +3815,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474281</v>
+        <v>474482</v>
       </c>
       <c r="R29" t="n">
-        <v>6849316</v>
+        <v>6849109</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3881,12 +3889,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3909,10 +3923,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118668282</v>
+        <v>118668265</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>79073</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3921,46 +3935,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474482</v>
+        <v>474281</v>
       </c>
       <c r="R30" t="n">
-        <v>6849109</v>
+        <v>6849316</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3995,18 +4001,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4029,10 +4029,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118668280</v>
+        <v>118668260</v>
       </c>
       <c r="B31" t="n">
-        <v>97846</v>
+        <v>78518</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4041,46 +4041,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474488</v>
+        <v>474477</v>
       </c>
       <c r="R31" t="n">
-        <v>6849095</v>
+        <v>6849113</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4115,18 +4107,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4149,10 +4135,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118668260</v>
+        <v>118668280</v>
       </c>
       <c r="B32" t="n">
-        <v>78518</v>
+        <v>97846</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4161,38 +4147,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474477</v>
+        <v>474488</v>
       </c>
       <c r="R32" t="n">
-        <v>6849113</v>
+        <v>6849095</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4227,12 +4221,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118668291</v>
+        <v>118668285</v>
       </c>
       <c r="B2" t="n">
         <v>97846</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474499</v>
+        <v>474508</v>
       </c>
       <c r="R2" t="n">
-        <v>6849233</v>
+        <v>6849041</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118668269</v>
+        <v>118668289</v>
       </c>
       <c r="B3" t="n">
-        <v>78221</v>
+        <v>97846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,38 +807,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474281</v>
+        <v>474510</v>
       </c>
       <c r="R3" t="n">
-        <v>6849315</v>
+        <v>6849050</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -873,12 +881,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118668295</v>
+        <v>118668304</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,46 +927,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474611</v>
+        <v>474501</v>
       </c>
       <c r="R4" t="n">
-        <v>6849103</v>
+        <v>6849066</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -987,18 +993,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118668290</v>
+        <v>118668266</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,46 +1033,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474513</v>
+        <v>474350</v>
       </c>
       <c r="R5" t="n">
-        <v>6849159</v>
+        <v>6849290</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1107,18 +1099,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118668296</v>
+        <v>118668292</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1189,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474344</v>
+        <v>474404</v>
       </c>
       <c r="R6" t="n">
-        <v>6849284</v>
+        <v>6849287</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1229,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118668277</v>
+        <v>118668305</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>78129</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,46 +1259,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474434</v>
+        <v>474253</v>
       </c>
       <c r="R7" t="n">
-        <v>6849105</v>
+        <v>6849332</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1347,18 +1325,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1381,7 +1353,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118668273</v>
+        <v>118668290</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1429,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474331</v>
+        <v>474513</v>
       </c>
       <c r="R8" t="n">
-        <v>6849334</v>
+        <v>6849159</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1501,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118668298</v>
+        <v>118668261</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,46 +1485,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474502</v>
+        <v>474296</v>
       </c>
       <c r="R9" t="n">
-        <v>6849036</v>
+        <v>6849305</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1587,18 +1551,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1621,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118668278</v>
+        <v>118668303</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,46 +1591,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474442</v>
+        <v>474498</v>
       </c>
       <c r="R10" t="n">
-        <v>6849111</v>
+        <v>6849066</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1707,18 +1657,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1741,7 +1685,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118668288</v>
+        <v>118668294</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1789,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474489</v>
+        <v>474399</v>
       </c>
       <c r="R11" t="n">
-        <v>6849017</v>
+        <v>6849297</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1829,7 +1773,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,7 +1805,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118668286</v>
+        <v>118668273</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1909,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474459</v>
+        <v>474331</v>
       </c>
       <c r="R12" t="n">
-        <v>6849011</v>
+        <v>6849334</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1981,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118668300</v>
+        <v>118668302</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1993,46 +1937,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474357</v>
+        <v>474448</v>
       </c>
       <c r="R13" t="n">
-        <v>6849288</v>
+        <v>6849112</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2067,18 +2003,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2101,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118668294</v>
+        <v>118668262</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2113,46 +2043,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474399</v>
+        <v>474285</v>
       </c>
       <c r="R14" t="n">
-        <v>6849297</v>
+        <v>6849320</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2187,18 +2109,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2221,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118668266</v>
+        <v>118668286</v>
       </c>
       <c r="B15" t="n">
-        <v>78221</v>
+        <v>97846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2233,38 +2149,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474350</v>
+        <v>474459</v>
       </c>
       <c r="R15" t="n">
-        <v>6849290</v>
+        <v>6849011</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2299,12 +2223,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2327,10 +2257,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118668303</v>
+        <v>118668291</v>
       </c>
       <c r="B16" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2339,38 +2269,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474498</v>
+        <v>474499</v>
       </c>
       <c r="R16" t="n">
-        <v>6849066</v>
+        <v>6849233</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2405,12 +2343,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2433,7 +2377,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118668297</v>
+        <v>118668287</v>
       </c>
       <c r="B17" t="n">
         <v>97846</v>
@@ -2481,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474456</v>
+        <v>474480</v>
       </c>
       <c r="R17" t="n">
-        <v>6849018</v>
+        <v>6849016</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2521,7 +2465,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2553,7 +2497,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118668292</v>
+        <v>118668296</v>
       </c>
       <c r="B18" t="n">
         <v>97846</v>
@@ -2601,10 +2545,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474404</v>
+        <v>474344</v>
       </c>
       <c r="R18" t="n">
-        <v>6849287</v>
+        <v>6849284</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2641,7 +2585,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>7 blomstjälkar</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,10 +2617,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118668285</v>
+        <v>118668269</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2685,46 +2629,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474508</v>
+        <v>474281</v>
       </c>
       <c r="R19" t="n">
-        <v>6849041</v>
+        <v>6849315</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2759,18 +2695,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2793,7 +2723,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118668287</v>
+        <v>118668277</v>
       </c>
       <c r="B20" t="n">
         <v>97846</v>
@@ -2841,10 +2771,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474480</v>
+        <v>474434</v>
       </c>
       <c r="R20" t="n">
-        <v>6849016</v>
+        <v>6849105</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2913,7 +2843,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118668301</v>
+        <v>118668297</v>
       </c>
       <c r="B21" t="n">
         <v>97846</v>
@@ -2947,16 +2877,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474347</v>
+        <v>474456</v>
       </c>
       <c r="R21" t="n">
-        <v>6849287</v>
+        <v>6849018</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2991,12 +2929,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3019,10 +2963,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118668276</v>
+        <v>118668271</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>78220</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3031,46 +2975,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474404</v>
+        <v>474250</v>
       </c>
       <c r="R22" t="n">
-        <v>6849098</v>
+        <v>6849335</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3105,18 +3041,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3139,10 +3069,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118668308</v>
+        <v>118668298</v>
       </c>
       <c r="B23" t="n">
-        <v>78129</v>
+        <v>97846</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3151,38 +3081,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474281</v>
+        <v>474502</v>
       </c>
       <c r="R23" t="n">
-        <v>6849312</v>
+        <v>6849036</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3217,12 +3155,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3245,10 +3189,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118668271</v>
+        <v>118668282</v>
       </c>
       <c r="B24" t="n">
-        <v>78220</v>
+        <v>97846</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3257,38 +3201,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474250</v>
+        <v>474482</v>
       </c>
       <c r="R24" t="n">
-        <v>6849335</v>
+        <v>6849109</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3323,12 +3275,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3351,10 +3309,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118668284</v>
+        <v>118668267</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3363,46 +3321,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474602</v>
+        <v>474296</v>
       </c>
       <c r="R25" t="n">
-        <v>6849096</v>
+        <v>6849305</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3437,18 +3387,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3471,10 +3415,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118668279</v>
+        <v>118668263</v>
       </c>
       <c r="B26" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3483,46 +3427,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474461</v>
+        <v>474253</v>
       </c>
       <c r="R26" t="n">
-        <v>6849116</v>
+        <v>6849332</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3557,18 +3493,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3591,10 +3521,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118668305</v>
+        <v>118668288</v>
       </c>
       <c r="B27" t="n">
-        <v>78129</v>
+        <v>97846</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3603,38 +3533,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474253</v>
+        <v>474489</v>
       </c>
       <c r="R27" t="n">
-        <v>6849332</v>
+        <v>6849017</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3669,12 +3607,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3697,10 +3641,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118668261</v>
+        <v>118668293</v>
       </c>
       <c r="B28" t="n">
-        <v>79102</v>
+        <v>97846</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3709,38 +3653,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474296</v>
+        <v>474329</v>
       </c>
       <c r="R28" t="n">
-        <v>6849305</v>
+        <v>6849322</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3775,12 +3727,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>5 blomtjälkar</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3803,10 +3761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118668282</v>
+        <v>118668265</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>79073</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3815,46 +3773,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474482</v>
+        <v>474281</v>
       </c>
       <c r="R29" t="n">
-        <v>6849109</v>
+        <v>6849316</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3889,18 +3839,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3923,10 +3867,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118668265</v>
+        <v>118668295</v>
       </c>
       <c r="B30" t="n">
-        <v>79073</v>
+        <v>97846</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3935,38 +3879,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474281</v>
+        <v>474611</v>
       </c>
       <c r="R30" t="n">
-        <v>6849316</v>
+        <v>6849103</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4001,12 +3953,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4029,10 +3987,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118668260</v>
+        <v>118668284</v>
       </c>
       <c r="B31" t="n">
-        <v>78518</v>
+        <v>97846</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4041,38 +3999,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474477</v>
+        <v>474602</v>
       </c>
       <c r="R31" t="n">
-        <v>6849113</v>
+        <v>6849096</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4107,12 +4073,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4135,7 +4107,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118668280</v>
+        <v>118668279</v>
       </c>
       <c r="B32" t="n">
         <v>97846</v>
@@ -4183,10 +4155,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474488</v>
+        <v>474461</v>
       </c>
       <c r="R32" t="n">
-        <v>6849095</v>
+        <v>6849116</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4255,10 +4227,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118668267</v>
+        <v>118668260</v>
       </c>
       <c r="B33" t="n">
-        <v>78221</v>
+        <v>78518</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4271,21 +4243,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4295,10 +4267,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474296</v>
+        <v>474477</v>
       </c>
       <c r="R33" t="n">
-        <v>6849305</v>
+        <v>6849113</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4361,10 +4333,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118668263</v>
+        <v>118668278</v>
       </c>
       <c r="B34" t="n">
-        <v>79102</v>
+        <v>97846</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4373,38 +4345,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474253</v>
+        <v>474442</v>
       </c>
       <c r="R34" t="n">
-        <v>6849332</v>
+        <v>6849111</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4439,12 +4419,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4467,7 +4453,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118668293</v>
+        <v>118668276</v>
       </c>
       <c r="B35" t="n">
         <v>97846</v>
@@ -4515,10 +4501,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474329</v>
+        <v>474404</v>
       </c>
       <c r="R35" t="n">
-        <v>6849322</v>
+        <v>6849098</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4555,7 +4541,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>5 blomtjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4587,10 +4573,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118668304</v>
+        <v>118668272</v>
       </c>
       <c r="B36" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4599,38 +4585,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474501</v>
+        <v>474499</v>
       </c>
       <c r="R36" t="n">
-        <v>6849066</v>
+        <v>6849218</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4665,12 +4659,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118668283</v>
+        <v>118668300</v>
       </c>
       <c r="B37" t="n">
         <v>97846</v>
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474330</v>
+        <v>474357</v>
       </c>
       <c r="R37" t="n">
-        <v>6849329</v>
+        <v>6849288</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4813,7 +4813,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118668272</v>
+        <v>118668283</v>
       </c>
       <c r="B38" t="n">
         <v>97846</v>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474499</v>
+        <v>474330</v>
       </c>
       <c r="R38" t="n">
-        <v>6849218</v>
+        <v>6849329</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4933,10 +4933,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118668289</v>
+        <v>118668308</v>
       </c>
       <c r="B39" t="n">
-        <v>97846</v>
+        <v>78129</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4945,46 +4945,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474510</v>
+        <v>474281</v>
       </c>
       <c r="R39" t="n">
-        <v>6849050</v>
+        <v>6849312</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5019,18 +5011,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5053,10 +5039,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118668302</v>
+        <v>118668280</v>
       </c>
       <c r="B40" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5065,38 +5051,46 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474448</v>
+        <v>474488</v>
       </c>
       <c r="R40" t="n">
-        <v>6849112</v>
+        <v>6849095</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5131,12 +5125,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118668262</v>
+        <v>118668301</v>
       </c>
       <c r="B41" t="n">
-        <v>79102</v>
+        <v>97846</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5171,25 +5171,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474285</v>
+        <v>474347</v>
       </c>
       <c r="R41" t="n">
-        <v>6849320</v>
+        <v>6849287</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118668294</v>
+        <v>118668302</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,46 +1697,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474399</v>
+        <v>474448</v>
       </c>
       <c r="R11" t="n">
-        <v>6849297</v>
+        <v>6849112</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1771,18 +1763,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1805,7 +1791,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118668273</v>
+        <v>118668294</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1853,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474331</v>
+        <v>474399</v>
       </c>
       <c r="R12" t="n">
-        <v>6849334</v>
+        <v>6849297</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1893,7 +1879,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118668302</v>
+        <v>118668273</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,38 +1923,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474448</v>
+        <v>474331</v>
       </c>
       <c r="R13" t="n">
-        <v>6849112</v>
+        <v>6849334</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2003,12 +1997,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118668262</v>
+        <v>118668286</v>
       </c>
       <c r="B14" t="n">
-        <v>79102</v>
+        <v>97846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,38 +2043,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474285</v>
+        <v>474459</v>
       </c>
       <c r="R14" t="n">
-        <v>6849320</v>
+        <v>6849011</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2109,12 +2117,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2137,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118668286</v>
+        <v>118668262</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2149,46 +2163,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474459</v>
+        <v>474285</v>
       </c>
       <c r="R15" t="n">
-        <v>6849011</v>
+        <v>6849320</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2223,18 +2229,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2723,10 +2723,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118668277</v>
+        <v>118668271</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>78220</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2735,46 +2735,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474434</v>
+        <v>474250</v>
       </c>
       <c r="R20" t="n">
-        <v>6849105</v>
+        <v>6849335</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2809,18 +2801,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2843,7 +2829,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118668297</v>
+        <v>118668277</v>
       </c>
       <c r="B21" t="n">
         <v>97846</v>
@@ -2891,10 +2877,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474456</v>
+        <v>474434</v>
       </c>
       <c r="R21" t="n">
-        <v>6849018</v>
+        <v>6849105</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2931,7 +2917,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,10 +2949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118668271</v>
+        <v>118668297</v>
       </c>
       <c r="B22" t="n">
-        <v>78220</v>
+        <v>97846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2975,38 +2961,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474250</v>
+        <v>474456</v>
       </c>
       <c r="R22" t="n">
-        <v>6849335</v>
+        <v>6849018</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3041,12 +3035,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -4693,10 +4693,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118668300</v>
+        <v>118668308</v>
       </c>
       <c r="B37" t="n">
-        <v>97846</v>
+        <v>78129</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4705,46 +4705,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474357</v>
+        <v>474281</v>
       </c>
       <c r="R37" t="n">
-        <v>6849288</v>
+        <v>6849312</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4779,18 +4771,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4813,7 +4799,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118668283</v>
+        <v>118668300</v>
       </c>
       <c r="B38" t="n">
         <v>97846</v>
@@ -4861,10 +4847,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474330</v>
+        <v>474357</v>
       </c>
       <c r="R38" t="n">
-        <v>6849329</v>
+        <v>6849288</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4901,7 +4887,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4933,10 +4919,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118668308</v>
+        <v>118668283</v>
       </c>
       <c r="B39" t="n">
-        <v>78129</v>
+        <v>97846</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4945,38 +4931,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474281</v>
+        <v>474330</v>
       </c>
       <c r="R39" t="n">
-        <v>6849312</v>
+        <v>6849329</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5011,12 +5005,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118668285</v>
+        <v>118668304</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474508</v>
+        <v>474501</v>
       </c>
       <c r="R2" t="n">
-        <v>6849041</v>
+        <v>6849066</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -761,18 +753,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118668289</v>
+        <v>118668262</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,46 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474510</v>
+        <v>474285</v>
       </c>
       <c r="R3" t="n">
-        <v>6849050</v>
+        <v>6849320</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -881,18 +859,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -915,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118668304</v>
+        <v>118668261</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474501</v>
+        <v>474296</v>
       </c>
       <c r="R4" t="n">
-        <v>6849066</v>
+        <v>6849305</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1021,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118668266</v>
+        <v>118668273</v>
       </c>
       <c r="B5" t="n">
-        <v>78221</v>
+        <v>97846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,38 +1005,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474350</v>
+        <v>474331</v>
       </c>
       <c r="R5" t="n">
-        <v>6849290</v>
+        <v>6849334</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1099,12 +1079,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118668292</v>
+        <v>118668271</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>78220</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,46 +1125,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474404</v>
+        <v>474250</v>
       </c>
       <c r="R6" t="n">
-        <v>6849287</v>
+        <v>6849335</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1213,18 +1191,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>7 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1247,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118668305</v>
+        <v>118668276</v>
       </c>
       <c r="B7" t="n">
-        <v>78129</v>
+        <v>97846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,38 +1231,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474253</v>
+        <v>474404</v>
       </c>
       <c r="R7" t="n">
-        <v>6849332</v>
+        <v>6849098</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1325,12 +1305,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1353,7 +1339,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118668290</v>
+        <v>118668286</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1401,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474513</v>
+        <v>474459</v>
       </c>
       <c r="R8" t="n">
-        <v>6849159</v>
+        <v>6849011</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1473,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118668261</v>
+        <v>118668295</v>
       </c>
       <c r="B9" t="n">
-        <v>79102</v>
+        <v>97846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,38 +1471,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474296</v>
+        <v>474611</v>
       </c>
       <c r="R9" t="n">
-        <v>6849305</v>
+        <v>6849103</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1551,12 +1545,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1579,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118668303</v>
+        <v>118668291</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,38 +1591,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474498</v>
+        <v>474499</v>
       </c>
       <c r="R10" t="n">
-        <v>6849066</v>
+        <v>6849233</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1657,12 +1665,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1685,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118668302</v>
+        <v>118668285</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,38 +1711,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474448</v>
+        <v>474508</v>
       </c>
       <c r="R11" t="n">
-        <v>6849112</v>
+        <v>6849041</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1763,12 +1785,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1791,7 +1819,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118668294</v>
+        <v>118668296</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1839,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474399</v>
+        <v>474344</v>
       </c>
       <c r="R12" t="n">
-        <v>6849297</v>
+        <v>6849284</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1879,7 +1907,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,7 +1939,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118668273</v>
+        <v>118668288</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -1959,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474331</v>
+        <v>474489</v>
       </c>
       <c r="R13" t="n">
-        <v>6849334</v>
+        <v>6849017</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2031,7 +2059,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118668286</v>
+        <v>118668280</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2079,10 +2107,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474459</v>
+        <v>474488</v>
       </c>
       <c r="R14" t="n">
-        <v>6849011</v>
+        <v>6849095</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2151,10 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118668262</v>
+        <v>118668293</v>
       </c>
       <c r="B15" t="n">
-        <v>79102</v>
+        <v>97846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2163,38 +2191,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474285</v>
+        <v>474329</v>
       </c>
       <c r="R15" t="n">
-        <v>6849320</v>
+        <v>6849322</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2229,12 +2265,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>5 blomtjälkar</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2257,10 +2299,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118668291</v>
+        <v>118668269</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,46 +2311,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474499</v>
+        <v>474281</v>
       </c>
       <c r="R16" t="n">
-        <v>6849233</v>
+        <v>6849315</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2343,18 +2377,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2497,7 +2525,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118668296</v>
+        <v>118668272</v>
       </c>
       <c r="B18" t="n">
         <v>97846</v>
@@ -2545,10 +2573,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474344</v>
+        <v>474499</v>
       </c>
       <c r="R18" t="n">
-        <v>6849284</v>
+        <v>6849218</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2585,7 +2613,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,10 +2645,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118668269</v>
+        <v>118668260</v>
       </c>
       <c r="B19" t="n">
-        <v>78221</v>
+        <v>78518</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,21 +2661,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2657,10 +2685,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474281</v>
+        <v>474477</v>
       </c>
       <c r="R19" t="n">
-        <v>6849315</v>
+        <v>6849113</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2723,10 +2751,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118668271</v>
+        <v>118668294</v>
       </c>
       <c r="B20" t="n">
-        <v>78220</v>
+        <v>97846</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2735,38 +2763,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474250</v>
+        <v>474399</v>
       </c>
       <c r="R20" t="n">
-        <v>6849335</v>
+        <v>6849297</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2801,12 +2837,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3069,7 +3111,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118668298</v>
+        <v>118668282</v>
       </c>
       <c r="B23" t="n">
         <v>97846</v>
@@ -3117,10 +3159,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474502</v>
+        <v>474482</v>
       </c>
       <c r="R23" t="n">
-        <v>6849036</v>
+        <v>6849109</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3157,7 +3199,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3189,10 +3231,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118668282</v>
+        <v>118668263</v>
       </c>
       <c r="B24" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3201,46 +3243,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474482</v>
+        <v>474253</v>
       </c>
       <c r="R24" t="n">
-        <v>6849109</v>
+        <v>6849332</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3275,18 +3309,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3309,10 +3337,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118668267</v>
+        <v>118668290</v>
       </c>
       <c r="B25" t="n">
-        <v>78221</v>
+        <v>97846</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3321,38 +3349,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474296</v>
+        <v>474513</v>
       </c>
       <c r="R25" t="n">
-        <v>6849305</v>
+        <v>6849159</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3387,12 +3423,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3415,10 +3457,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118668263</v>
+        <v>118668267</v>
       </c>
       <c r="B26" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3431,21 +3473,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3455,10 +3497,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474253</v>
+        <v>474296</v>
       </c>
       <c r="R26" t="n">
-        <v>6849332</v>
+        <v>6849305</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3521,10 +3563,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118668288</v>
+        <v>118668266</v>
       </c>
       <c r="B27" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3533,46 +3575,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474489</v>
+        <v>474350</v>
       </c>
       <c r="R27" t="n">
-        <v>6849017</v>
+        <v>6849290</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3607,18 +3641,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3641,10 +3669,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118668293</v>
+        <v>118668265</v>
       </c>
       <c r="B28" t="n">
-        <v>97846</v>
+        <v>79073</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3653,46 +3681,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474329</v>
+        <v>474281</v>
       </c>
       <c r="R28" t="n">
-        <v>6849322</v>
+        <v>6849316</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3727,18 +3747,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>5 blomtjälkar</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3761,10 +3775,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118668265</v>
+        <v>118668278</v>
       </c>
       <c r="B29" t="n">
-        <v>79073</v>
+        <v>97846</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3773,38 +3787,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474281</v>
+        <v>474442</v>
       </c>
       <c r="R29" t="n">
-        <v>6849316</v>
+        <v>6849111</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3839,12 +3861,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3867,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118668295</v>
+        <v>118668302</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3879,46 +3907,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474611</v>
+        <v>474448</v>
       </c>
       <c r="R30" t="n">
-        <v>6849103</v>
+        <v>6849112</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3953,18 +3973,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3987,7 +4001,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118668284</v>
+        <v>118668279</v>
       </c>
       <c r="B31" t="n">
         <v>97846</v>
@@ -4035,10 +4049,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474602</v>
+        <v>474461</v>
       </c>
       <c r="R31" t="n">
-        <v>6849096</v>
+        <v>6849116</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4107,7 +4121,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118668279</v>
+        <v>118668289</v>
       </c>
       <c r="B32" t="n">
         <v>97846</v>
@@ -4155,10 +4169,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474461</v>
+        <v>474510</v>
       </c>
       <c r="R32" t="n">
-        <v>6849116</v>
+        <v>6849050</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4227,10 +4241,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118668260</v>
+        <v>118668303</v>
       </c>
       <c r="B33" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4243,21 +4257,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4267,10 +4281,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474477</v>
+        <v>474498</v>
       </c>
       <c r="R33" t="n">
-        <v>6849113</v>
+        <v>6849066</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4333,7 +4347,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118668278</v>
+        <v>118668292</v>
       </c>
       <c r="B34" t="n">
         <v>97846</v>
@@ -4381,10 +4395,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474442</v>
+        <v>474404</v>
       </c>
       <c r="R34" t="n">
-        <v>6849111</v>
+        <v>6849287</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4421,7 +4435,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4453,7 +4467,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118668276</v>
+        <v>118668300</v>
       </c>
       <c r="B35" t="n">
         <v>97846</v>
@@ -4501,10 +4515,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474404</v>
+        <v>474357</v>
       </c>
       <c r="R35" t="n">
-        <v>6849098</v>
+        <v>6849288</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4541,7 +4555,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4573,7 +4587,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118668272</v>
+        <v>118668283</v>
       </c>
       <c r="B36" t="n">
         <v>97846</v>
@@ -4621,10 +4635,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474499</v>
+        <v>474330</v>
       </c>
       <c r="R36" t="n">
-        <v>6849218</v>
+        <v>6849329</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4799,7 +4813,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118668300</v>
+        <v>118668301</v>
       </c>
       <c r="B38" t="n">
         <v>97846</v>
@@ -4833,24 +4847,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474357</v>
+        <v>474347</v>
       </c>
       <c r="R38" t="n">
-        <v>6849288</v>
+        <v>6849287</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4885,18 +4891,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4919,10 +4919,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118668283</v>
+        <v>118668305</v>
       </c>
       <c r="B39" t="n">
-        <v>97846</v>
+        <v>78129</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4931,46 +4931,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474330</v>
+        <v>474253</v>
       </c>
       <c r="R39" t="n">
-        <v>6849329</v>
+        <v>6849332</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5005,18 +4997,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5039,7 +5025,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118668280</v>
+        <v>118668298</v>
       </c>
       <c r="B40" t="n">
         <v>97846</v>
@@ -5087,10 +5073,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474488</v>
+        <v>474502</v>
       </c>
       <c r="R40" t="n">
-        <v>6849095</v>
+        <v>6849036</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5127,7 +5113,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5159,7 +5145,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118668301</v>
+        <v>118668284</v>
       </c>
       <c r="B41" t="n">
         <v>97846</v>
@@ -5193,16 +5179,24 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474347</v>
+        <v>474602</v>
       </c>
       <c r="R41" t="n">
-        <v>6849287</v>
+        <v>6849096</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5237,12 +5231,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118668304</v>
+        <v>118668302</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474501</v>
+        <v>474448</v>
       </c>
       <c r="R2" t="n">
-        <v>6849066</v>
+        <v>6849112</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118668262</v>
+        <v>118668287</v>
       </c>
       <c r="B3" t="n">
-        <v>79102</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474285</v>
+        <v>474480</v>
       </c>
       <c r="R3" t="n">
-        <v>6849320</v>
+        <v>6849016</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -859,12 +867,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118668261</v>
+        <v>118668277</v>
       </c>
       <c r="B4" t="n">
-        <v>79102</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +913,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474296</v>
+        <v>474434</v>
       </c>
       <c r="R4" t="n">
-        <v>6849305</v>
+        <v>6849105</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,12 +987,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118668273</v>
+        <v>118668282</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474331</v>
+        <v>474482</v>
       </c>
       <c r="R5" t="n">
-        <v>6849334</v>
+        <v>6849109</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1113,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118668271</v>
+        <v>118668280</v>
       </c>
       <c r="B6" t="n">
-        <v>78220</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,38 +1153,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474250</v>
+        <v>474488</v>
       </c>
       <c r="R6" t="n">
-        <v>6849335</v>
+        <v>6849095</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1191,12 +1227,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1219,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118668276</v>
+        <v>118668291</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474404</v>
+        <v>474499</v>
       </c>
       <c r="R7" t="n">
-        <v>6849098</v>
+        <v>6849233</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1339,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118668286</v>
+        <v>118668273</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474459</v>
+        <v>474331</v>
       </c>
       <c r="R8" t="n">
-        <v>6849011</v>
+        <v>6849334</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1459,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118668295</v>
+        <v>118668263</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>79109</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,46 +1513,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474611</v>
+        <v>474253</v>
       </c>
       <c r="R9" t="n">
-        <v>6849103</v>
+        <v>6849332</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1545,18 +1579,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1579,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118668291</v>
+        <v>118668296</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474499</v>
+        <v>474344</v>
       </c>
       <c r="R10" t="n">
-        <v>6849233</v>
+        <v>6849284</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1667,7 +1695,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118668285</v>
+        <v>118668298</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474508</v>
+        <v>474502</v>
       </c>
       <c r="R11" t="n">
-        <v>6849041</v>
+        <v>6849036</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1787,7 +1815,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,10 +1847,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118668296</v>
+        <v>118668269</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>78228</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,46 +1859,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474344</v>
+        <v>474281</v>
       </c>
       <c r="R12" t="n">
-        <v>6849284</v>
+        <v>6849315</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1905,18 +1925,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1939,10 +1953,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118668288</v>
+        <v>118668303</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>78491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,46 +1965,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474489</v>
+        <v>474498</v>
       </c>
       <c r="R13" t="n">
-        <v>6849017</v>
+        <v>6849066</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2025,18 +2031,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2059,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118668280</v>
+        <v>118668290</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474488</v>
+        <v>474513</v>
       </c>
       <c r="R14" t="n">
-        <v>6849095</v>
+        <v>6849159</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2179,10 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118668293</v>
+        <v>118668300</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474329</v>
+        <v>474357</v>
       </c>
       <c r="R15" t="n">
-        <v>6849322</v>
+        <v>6849288</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5 blomtjälkar</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,10 +2299,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118668269</v>
+        <v>118668292</v>
       </c>
       <c r="B16" t="n">
-        <v>78221</v>
+        <v>97853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2311,38 +2311,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474281</v>
+        <v>474404</v>
       </c>
       <c r="R16" t="n">
-        <v>6849315</v>
+        <v>6849287</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2377,12 +2385,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>7 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2405,10 +2419,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118668287</v>
+        <v>118668284</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2453,10 +2467,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474480</v>
+        <v>474602</v>
       </c>
       <c r="R17" t="n">
-        <v>6849016</v>
+        <v>6849096</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2525,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118668272</v>
+        <v>118668265</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>79080</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2537,46 +2551,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474499</v>
+        <v>474281</v>
       </c>
       <c r="R18" t="n">
-        <v>6849218</v>
+        <v>6849316</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2611,18 +2617,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118668260</v>
+        <v>118668294</v>
       </c>
       <c r="B19" t="n">
-        <v>78518</v>
+        <v>97853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2657,38 +2657,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474477</v>
+        <v>474399</v>
       </c>
       <c r="R19" t="n">
-        <v>6849113</v>
+        <v>6849297</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2723,12 +2731,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2751,10 +2765,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118668294</v>
+        <v>118668289</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2799,10 +2813,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474399</v>
+        <v>474510</v>
       </c>
       <c r="R20" t="n">
-        <v>6849297</v>
+        <v>6849050</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2839,7 +2853,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2871,10 +2885,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118668277</v>
+        <v>118668261</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
+        <v>79109</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2883,46 +2897,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474434</v>
+        <v>474296</v>
       </c>
       <c r="R21" t="n">
-        <v>6849105</v>
+        <v>6849305</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2957,18 +2963,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118668297</v>
+        <v>118668271</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>78227</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3003,46 +3003,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474456</v>
+        <v>474250</v>
       </c>
       <c r="R22" t="n">
-        <v>6849018</v>
+        <v>6849335</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3077,18 +3069,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3111,10 +3097,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118668282</v>
+        <v>118668260</v>
       </c>
       <c r="B23" t="n">
-        <v>97846</v>
+        <v>78525</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3123,46 +3109,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474482</v>
+        <v>474477</v>
       </c>
       <c r="R23" t="n">
-        <v>6849109</v>
+        <v>6849113</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3197,18 +3175,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3231,10 +3203,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118668263</v>
+        <v>118668297</v>
       </c>
       <c r="B24" t="n">
-        <v>79102</v>
+        <v>97853</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3243,38 +3215,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474253</v>
+        <v>474456</v>
       </c>
       <c r="R24" t="n">
-        <v>6849332</v>
+        <v>6849018</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3309,12 +3289,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3337,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118668290</v>
+        <v>118668278</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3385,10 +3371,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474513</v>
+        <v>474442</v>
       </c>
       <c r="R25" t="n">
-        <v>6849159</v>
+        <v>6849111</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3457,10 +3443,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118668267</v>
+        <v>118668293</v>
       </c>
       <c r="B26" t="n">
-        <v>78221</v>
+        <v>97853</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3469,38 +3455,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474296</v>
+        <v>474329</v>
       </c>
       <c r="R26" t="n">
-        <v>6849305</v>
+        <v>6849322</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3535,12 +3529,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>5 blomtjälkar</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118668266</v>
+        <v>118668276</v>
       </c>
       <c r="B27" t="n">
-        <v>78221</v>
+        <v>97853</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3575,38 +3575,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474350</v>
+        <v>474404</v>
       </c>
       <c r="R27" t="n">
-        <v>6849290</v>
+        <v>6849098</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3641,12 +3649,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3669,10 +3683,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118668265</v>
+        <v>118668305</v>
       </c>
       <c r="B28" t="n">
-        <v>79073</v>
+        <v>78136</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3685,21 +3699,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3709,10 +3723,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474281</v>
+        <v>474253</v>
       </c>
       <c r="R28" t="n">
-        <v>6849316</v>
+        <v>6849332</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3775,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118668278</v>
+        <v>118668295</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3823,10 +3837,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474442</v>
+        <v>474611</v>
       </c>
       <c r="R29" t="n">
-        <v>6849111</v>
+        <v>6849103</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3863,7 +3877,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,10 +3909,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118668302</v>
+        <v>118668283</v>
       </c>
       <c r="B30" t="n">
-        <v>78484</v>
+        <v>97853</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3907,38 +3921,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474448</v>
+        <v>474330</v>
       </c>
       <c r="R30" t="n">
-        <v>6849112</v>
+        <v>6849329</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3973,12 +3995,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4001,10 +4029,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118668279</v>
+        <v>118668286</v>
       </c>
       <c r="B31" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4049,10 +4077,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474461</v>
+        <v>474459</v>
       </c>
       <c r="R31" t="n">
-        <v>6849116</v>
+        <v>6849011</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4121,10 +4149,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118668289</v>
+        <v>118668285</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4169,10 +4197,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474510</v>
+        <v>474508</v>
       </c>
       <c r="R32" t="n">
-        <v>6849050</v>
+        <v>6849041</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4241,10 +4269,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118668303</v>
+        <v>118668279</v>
       </c>
       <c r="B33" t="n">
-        <v>78484</v>
+        <v>97853</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4253,38 +4281,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474498</v>
+        <v>474461</v>
       </c>
       <c r="R33" t="n">
-        <v>6849066</v>
+        <v>6849116</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4319,12 +4355,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4347,10 +4389,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118668292</v>
+        <v>118668272</v>
       </c>
       <c r="B34" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4395,10 +4437,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474404</v>
+        <v>474499</v>
       </c>
       <c r="R34" t="n">
-        <v>6849287</v>
+        <v>6849218</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4435,7 +4477,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>7 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4467,10 +4509,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118668300</v>
+        <v>118668267</v>
       </c>
       <c r="B35" t="n">
-        <v>97846</v>
+        <v>78228</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4479,46 +4521,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474357</v>
+        <v>474296</v>
       </c>
       <c r="R35" t="n">
-        <v>6849288</v>
+        <v>6849305</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4553,18 +4587,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4587,10 +4615,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118668283</v>
+        <v>118668262</v>
       </c>
       <c r="B36" t="n">
-        <v>97846</v>
+        <v>79109</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4599,46 +4627,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474330</v>
+        <v>474285</v>
       </c>
       <c r="R36" t="n">
-        <v>6849329</v>
+        <v>6849320</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4673,18 +4693,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4707,10 +4721,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118668308</v>
+        <v>118668288</v>
       </c>
       <c r="B37" t="n">
-        <v>78129</v>
+        <v>97853</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4719,38 +4733,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474281</v>
+        <v>474489</v>
       </c>
       <c r="R37" t="n">
-        <v>6849312</v>
+        <v>6849017</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4785,12 +4807,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4813,10 +4841,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118668301</v>
+        <v>118668266</v>
       </c>
       <c r="B38" t="n">
-        <v>97846</v>
+        <v>78228</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4825,25 +4853,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4853,10 +4881,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474347</v>
+        <v>474350</v>
       </c>
       <c r="R38" t="n">
-        <v>6849287</v>
+        <v>6849290</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4919,10 +4947,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118668305</v>
+        <v>118668308</v>
       </c>
       <c r="B39" t="n">
-        <v>78129</v>
+        <v>78136</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4959,10 +4987,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474253</v>
+        <v>474281</v>
       </c>
       <c r="R39" t="n">
-        <v>6849332</v>
+        <v>6849312</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5025,10 +5053,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118668298</v>
+        <v>118668304</v>
       </c>
       <c r="B40" t="n">
-        <v>97846</v>
+        <v>78491</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5037,46 +5065,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474502</v>
+        <v>474501</v>
       </c>
       <c r="R40" t="n">
-        <v>6849036</v>
+        <v>6849066</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5111,18 +5131,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5145,10 +5159,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118668284</v>
+        <v>118668301</v>
       </c>
       <c r="B41" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5179,24 +5193,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474602</v>
+        <v>474347</v>
       </c>
       <c r="R41" t="n">
-        <v>6849096</v>
+        <v>6849287</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5231,18 +5237,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -1607,7 +1607,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118668296</v>
+        <v>118668298</v>
       </c>
       <c r="B10" t="n">
         <v>97853</v>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474344</v>
+        <v>474502</v>
       </c>
       <c r="R10" t="n">
-        <v>6849284</v>
+        <v>6849036</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118668298</v>
+        <v>118668269</v>
       </c>
       <c r="B11" t="n">
-        <v>97853</v>
+        <v>78228</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,46 +1739,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474502</v>
+        <v>474281</v>
       </c>
       <c r="R11" t="n">
-        <v>6849036</v>
+        <v>6849315</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1813,18 +1805,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1847,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118668269</v>
+        <v>118668296</v>
       </c>
       <c r="B12" t="n">
-        <v>78228</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,38 +1845,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474281</v>
+        <v>474344</v>
       </c>
       <c r="R12" t="n">
-        <v>6849315</v>
+        <v>6849284</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1925,12 +1919,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -4947,10 +4947,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118668308</v>
+        <v>118668304</v>
       </c>
       <c r="B39" t="n">
-        <v>78136</v>
+        <v>78491</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4963,21 +4963,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4987,10 +4987,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474281</v>
+        <v>474501</v>
       </c>
       <c r="R39" t="n">
-        <v>6849312</v>
+        <v>6849066</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5053,10 +5053,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118668304</v>
+        <v>118668301</v>
       </c>
       <c r="B40" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5065,25 +5065,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474501</v>
+        <v>474347</v>
       </c>
       <c r="R40" t="n">
-        <v>6849066</v>
+        <v>6849287</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118668301</v>
+        <v>118668308</v>
       </c>
       <c r="B41" t="n">
-        <v>97853</v>
+        <v>78136</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5171,25 +5171,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474347</v>
+        <v>474281</v>
       </c>
       <c r="R41" t="n">
-        <v>6849287</v>
+        <v>6849312</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118668302</v>
+        <v>118668308</v>
       </c>
       <c r="B2" t="n">
-        <v>78491</v>
+        <v>78136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474448</v>
+        <v>474281</v>
       </c>
       <c r="R2" t="n">
-        <v>6849112</v>
+        <v>6849312</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118668287</v>
+        <v>118668266</v>
       </c>
       <c r="B3" t="n">
-        <v>97853</v>
+        <v>78228</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,46 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474480</v>
+        <v>474350</v>
       </c>
       <c r="R3" t="n">
-        <v>6849016</v>
+        <v>6849290</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -867,18 +859,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118668277</v>
+        <v>118668289</v>
       </c>
       <c r="B4" t="n">
         <v>97853</v>
@@ -949,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474434</v>
+        <v>474510</v>
       </c>
       <c r="R4" t="n">
-        <v>6849105</v>
+        <v>6849050</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1021,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118668282</v>
+        <v>118668261</v>
       </c>
       <c r="B5" t="n">
-        <v>97853</v>
+        <v>79109</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,46 +1019,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474482</v>
+        <v>474296</v>
       </c>
       <c r="R5" t="n">
-        <v>6849109</v>
+        <v>6849305</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1107,18 +1085,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118668280</v>
+        <v>118668263</v>
       </c>
       <c r="B6" t="n">
-        <v>97853</v>
+        <v>79109</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,46 +1125,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474488</v>
+        <v>474253</v>
       </c>
       <c r="R6" t="n">
-        <v>6849095</v>
+        <v>6849332</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1227,18 +1191,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1261,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118668291</v>
+        <v>118668297</v>
       </c>
       <c r="B7" t="n">
         <v>97853</v>
@@ -1309,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474499</v>
+        <v>474456</v>
       </c>
       <c r="R7" t="n">
-        <v>6849233</v>
+        <v>6849018</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1349,7 +1307,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,7 +1339,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118668273</v>
+        <v>118668293</v>
       </c>
       <c r="B8" t="n">
         <v>97853</v>
@@ -1429,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474331</v>
+        <v>474329</v>
       </c>
       <c r="R8" t="n">
-        <v>6849334</v>
+        <v>6849322</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1469,7 +1427,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>5 blomtjälkar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118668263</v>
+        <v>118668284</v>
       </c>
       <c r="B9" t="n">
-        <v>79109</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,38 +1471,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474253</v>
+        <v>474602</v>
       </c>
       <c r="R9" t="n">
-        <v>6849332</v>
+        <v>6849096</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1579,12 +1545,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1607,7 +1579,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118668298</v>
+        <v>118668288</v>
       </c>
       <c r="B10" t="n">
         <v>97853</v>
@@ -1655,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474502</v>
+        <v>474489</v>
       </c>
       <c r="R10" t="n">
-        <v>6849036</v>
+        <v>6849017</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1695,7 +1667,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118668269</v>
+        <v>118668260</v>
       </c>
       <c r="B11" t="n">
-        <v>78228</v>
+        <v>78525</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1767,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474281</v>
+        <v>474477</v>
       </c>
       <c r="R11" t="n">
-        <v>6849315</v>
+        <v>6849113</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1833,7 +1805,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118668296</v>
+        <v>118668291</v>
       </c>
       <c r="B12" t="n">
         <v>97853</v>
@@ -1881,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474344</v>
+        <v>474499</v>
       </c>
       <c r="R12" t="n">
-        <v>6849284</v>
+        <v>6849233</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1921,7 +1893,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1953,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118668303</v>
+        <v>118668273</v>
       </c>
       <c r="B13" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1965,38 +1937,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474498</v>
+        <v>474331</v>
       </c>
       <c r="R13" t="n">
-        <v>6849066</v>
+        <v>6849334</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2031,12 +2011,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2059,7 +2045,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118668290</v>
+        <v>118668279</v>
       </c>
       <c r="B14" t="n">
         <v>97853</v>
@@ -2107,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474513</v>
+        <v>474461</v>
       </c>
       <c r="R14" t="n">
-        <v>6849159</v>
+        <v>6849116</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2179,7 +2165,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118668300</v>
+        <v>118668294</v>
       </c>
       <c r="B15" t="n">
         <v>97853</v>
@@ -2227,10 +2213,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474357</v>
+        <v>474399</v>
       </c>
       <c r="R15" t="n">
-        <v>6849288</v>
+        <v>6849297</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2267,7 +2253,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2419,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118668284</v>
+        <v>118668271</v>
       </c>
       <c r="B17" t="n">
-        <v>97853</v>
+        <v>78227</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,46 +2417,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474602</v>
+        <v>474250</v>
       </c>
       <c r="R17" t="n">
-        <v>6849096</v>
+        <v>6849335</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2505,18 +2483,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2645,7 +2617,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118668294</v>
+        <v>118668278</v>
       </c>
       <c r="B19" t="n">
         <v>97853</v>
@@ -2693,10 +2665,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474399</v>
+        <v>474442</v>
       </c>
       <c r="R19" t="n">
-        <v>6849297</v>
+        <v>6849111</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2733,7 +2705,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,7 +2737,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118668289</v>
+        <v>118668300</v>
       </c>
       <c r="B20" t="n">
         <v>97853</v>
@@ -2813,10 +2785,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474510</v>
+        <v>474357</v>
       </c>
       <c r="R20" t="n">
-        <v>6849050</v>
+        <v>6849288</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2853,7 +2825,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2885,10 +2857,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118668261</v>
+        <v>118668272</v>
       </c>
       <c r="B21" t="n">
-        <v>79109</v>
+        <v>97853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2897,38 +2869,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474296</v>
+        <v>474499</v>
       </c>
       <c r="R21" t="n">
-        <v>6849305</v>
+        <v>6849218</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2963,12 +2943,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2991,10 +2977,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118668271</v>
+        <v>118668277</v>
       </c>
       <c r="B22" t="n">
-        <v>78227</v>
+        <v>97853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3003,38 +2989,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474250</v>
+        <v>474434</v>
       </c>
       <c r="R22" t="n">
-        <v>6849335</v>
+        <v>6849105</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3069,12 +3063,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3097,10 +3097,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118668260</v>
+        <v>118668283</v>
       </c>
       <c r="B23" t="n">
-        <v>78525</v>
+        <v>97853</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3109,38 +3109,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474477</v>
+        <v>474330</v>
       </c>
       <c r="R23" t="n">
-        <v>6849113</v>
+        <v>6849329</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3175,12 +3183,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3203,7 +3217,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118668297</v>
+        <v>118668280</v>
       </c>
       <c r="B24" t="n">
         <v>97853</v>
@@ -3251,10 +3265,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474456</v>
+        <v>474488</v>
       </c>
       <c r="R24" t="n">
-        <v>6849018</v>
+        <v>6849095</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3291,7 +3305,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,7 +3337,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118668278</v>
+        <v>118668286</v>
       </c>
       <c r="B25" t="n">
         <v>97853</v>
@@ -3371,10 +3385,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474442</v>
+        <v>474459</v>
       </c>
       <c r="R25" t="n">
-        <v>6849111</v>
+        <v>6849011</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3443,10 +3457,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118668293</v>
+        <v>118668302</v>
       </c>
       <c r="B26" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3455,46 +3469,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474329</v>
+        <v>474448</v>
       </c>
       <c r="R26" t="n">
-        <v>6849322</v>
+        <v>6849112</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3529,18 +3535,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>5 blomtjälkar</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3563,7 +3563,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118668276</v>
+        <v>118668285</v>
       </c>
       <c r="B27" t="n">
         <v>97853</v>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474404</v>
+        <v>474508</v>
       </c>
       <c r="R27" t="n">
-        <v>6849098</v>
+        <v>6849041</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3683,10 +3683,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118668305</v>
+        <v>118668269</v>
       </c>
       <c r="B28" t="n">
-        <v>78136</v>
+        <v>78228</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474253</v>
+        <v>474281</v>
       </c>
       <c r="R28" t="n">
-        <v>6849332</v>
+        <v>6849315</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3789,7 +3789,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118668295</v>
+        <v>118668296</v>
       </c>
       <c r="B29" t="n">
         <v>97853</v>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474611</v>
+        <v>474344</v>
       </c>
       <c r="R29" t="n">
-        <v>6849103</v>
+        <v>6849284</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3909,7 +3909,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118668283</v>
+        <v>118668287</v>
       </c>
       <c r="B30" t="n">
         <v>97853</v>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474330</v>
+        <v>474480</v>
       </c>
       <c r="R30" t="n">
-        <v>6849329</v>
+        <v>6849016</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4029,10 +4029,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118668286</v>
+        <v>118668304</v>
       </c>
       <c r="B31" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4041,46 +4041,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474459</v>
+        <v>474501</v>
       </c>
       <c r="R31" t="n">
-        <v>6849011</v>
+        <v>6849066</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4115,18 +4107,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4149,7 +4135,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118668285</v>
+        <v>118668282</v>
       </c>
       <c r="B32" t="n">
         <v>97853</v>
@@ -4197,10 +4183,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474508</v>
+        <v>474482</v>
       </c>
       <c r="R32" t="n">
-        <v>6849041</v>
+        <v>6849109</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4269,7 +4255,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118668279</v>
+        <v>118668298</v>
       </c>
       <c r="B33" t="n">
         <v>97853</v>
@@ -4317,10 +4303,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474461</v>
+        <v>474502</v>
       </c>
       <c r="R33" t="n">
-        <v>6849116</v>
+        <v>6849036</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4357,7 +4343,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4389,7 +4375,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118668272</v>
+        <v>118668301</v>
       </c>
       <c r="B34" t="n">
         <v>97853</v>
@@ -4423,24 +4409,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474499</v>
+        <v>474347</v>
       </c>
       <c r="R34" t="n">
-        <v>6849218</v>
+        <v>6849287</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4475,18 +4453,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4615,10 +4587,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118668262</v>
+        <v>118668303</v>
       </c>
       <c r="B36" t="n">
-        <v>79109</v>
+        <v>78491</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4631,21 +4603,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4655,10 +4627,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474285</v>
+        <v>474498</v>
       </c>
       <c r="R36" t="n">
-        <v>6849320</v>
+        <v>6849066</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4721,7 +4693,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118668288</v>
+        <v>118668290</v>
       </c>
       <c r="B37" t="n">
         <v>97853</v>
@@ -4769,10 +4741,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474489</v>
+        <v>474513</v>
       </c>
       <c r="R37" t="n">
-        <v>6849017</v>
+        <v>6849159</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4841,10 +4813,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118668266</v>
+        <v>118668276</v>
       </c>
       <c r="B38" t="n">
-        <v>78228</v>
+        <v>97853</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4853,38 +4825,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474350</v>
+        <v>474404</v>
       </c>
       <c r="R38" t="n">
-        <v>6849290</v>
+        <v>6849098</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4919,12 +4899,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4947,10 +4933,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118668304</v>
+        <v>118668305</v>
       </c>
       <c r="B39" t="n">
-        <v>78491</v>
+        <v>78136</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4963,21 +4949,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4987,10 +4973,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474501</v>
+        <v>474253</v>
       </c>
       <c r="R39" t="n">
-        <v>6849066</v>
+        <v>6849332</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5053,10 +5039,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118668301</v>
+        <v>118668262</v>
       </c>
       <c r="B40" t="n">
-        <v>97853</v>
+        <v>79109</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5065,25 +5051,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5093,10 +5079,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474347</v>
+        <v>474285</v>
       </c>
       <c r="R40" t="n">
-        <v>6849287</v>
+        <v>6849320</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5159,10 +5145,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118668308</v>
+        <v>118668295</v>
       </c>
       <c r="B41" t="n">
-        <v>78136</v>
+        <v>97853</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5171,38 +5157,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474281</v>
+        <v>474611</v>
       </c>
       <c r="R41" t="n">
-        <v>6849312</v>
+        <v>6849103</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5237,12 +5231,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5262,6 +5262,874 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127362304</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>474663</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6848747</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127362966</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>474752</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6848680</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127362991</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>474773</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6848689</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1 blommande</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127362853</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>474748</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6848724</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>3 blommande</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127362917</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bergmyran, Bergmyran, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>474781</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6848688</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127363562</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>474691</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6848604</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127362641</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>474710</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6848736</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127362771</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>474749</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6848712</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5265,10 +5265,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127362304</v>
+        <v>127362966</v>
       </c>
       <c r="B42" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5309,13 +5309,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474663</v>
+        <v>474752</v>
       </c>
       <c r="R42" t="n">
-        <v>6848747</v>
+        <v>6848680</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5342,9 +5342,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5359,22 +5369,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127362966</v>
+        <v>127362304</v>
       </c>
       <c r="B43" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5401,12 +5411,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5415,13 +5425,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474752</v>
+        <v>474663</v>
       </c>
       <c r="R43" t="n">
-        <v>6848680</v>
+        <v>6848747</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5448,19 +5458,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5475,12 +5475,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5490,7 +5490,7 @@
         <v>127362991</v>
       </c>
       <c r="B44" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>127362853</v>
       </c>
       <c r="B45" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>127362917</v>
       </c>
       <c r="B46" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127363562</v>
       </c>
       <c r="B47" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127362641</v>
+        <v>127362771</v>
       </c>
       <c r="B48" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474710</v>
+        <v>474749</v>
       </c>
       <c r="R48" t="n">
-        <v>6848736</v>
+        <v>6848712</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6027,10 +6027,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127362771</v>
+        <v>127362641</v>
       </c>
       <c r="B49" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474749</v>
+        <v>474710</v>
       </c>
       <c r="R49" t="n">
-        <v>6848712</v>
+        <v>6848736</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6130,6 +6130,3896 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127363457</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>474724</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6848681</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127402375</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>474605</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6848875</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127362672</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>474728</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6848726</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127386307</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>474736</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6848669</v>
+      </c>
+      <c r="S53" t="n">
+        <v>4</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127363005</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>474656</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6848946</v>
+      </c>
+      <c r="S54" t="n">
+        <v>4</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127402796</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79046</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>185</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>474724</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6848762</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127402478</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>474626</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6848851</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127362687</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>474755</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6848852</v>
+      </c>
+      <c r="S57" t="n">
+        <v>4</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127362535</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>474796</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6848733</v>
+      </c>
+      <c r="S58" t="n">
+        <v>4</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127361760</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>474655</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6848869</v>
+      </c>
+      <c r="S59" t="n">
+        <v>4</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127361676</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79046</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>185</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>474659</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6848942</v>
+      </c>
+      <c r="S60" t="n">
+        <v>4</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127361806</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>474668</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6848864</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127362598</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>474703</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6848747</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127363240</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>474737</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6848663</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127362191</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>474687</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6848753</v>
+      </c>
+      <c r="S64" t="n">
+        <v>4</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127363437</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>474725</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6848676</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127361820</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>474667</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6848863</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127361703</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>474655</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6848935</v>
+      </c>
+      <c r="S67" t="n">
+        <v>4</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127362891</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>474768</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6848772</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127362521</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>474703</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6848742</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127362960</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>474647</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6848955</v>
+      </c>
+      <c r="S70" t="n">
+        <v>4</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127363059</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>474726</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6848721</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127362832</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>474744</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6848705</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127362075</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91291</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>474667</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6848863</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127363018</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>474754</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6848679</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127362721</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>474740</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6848725</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>127362532</v>
+      </c>
+      <c r="B76" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>474704</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6848745</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127363816</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>474651</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6848722</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127362954</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>474761</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6848679</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127363287</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>474728</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6848674</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>127362906</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>474761</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6848715</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127363073</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>474727</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6848702</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127362816</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>474739</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6848699</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127363338</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>474730</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6848680</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127402462</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>474630</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6848862</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -6341,7 +6341,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127362672</v>
+        <v>127386307</v>
       </c>
       <c r="B52" t="n">
         <v>98443</v>
@@ -6371,27 +6371,26 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kontoret, Kontoret, Hjd</t>
+          <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474728</v>
+        <v>474736</v>
       </c>
       <c r="R52" t="n">
-        <v>6848726</v>
+        <v>6848669</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6418,46 +6417,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127386307</v>
+        <v>127362672</v>
       </c>
       <c r="B53" t="n">
         <v>98443</v>
@@ -6487,26 +6477,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474736</v>
+        <v>474728</v>
       </c>
       <c r="R53" t="n">
-        <v>6848669</v>
+        <v>6848726</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,30 +6524,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -8912,7 +8912,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127362721</v>
+        <v>127363816</v>
       </c>
       <c r="B75" t="n">
         <v>98443</v>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>474740</v>
+        <v>474651</v>
       </c>
       <c r="R75" t="n">
-        <v>6848725</v>
+        <v>6848722</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9016,14 +9016,14 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127362532</v>
+        <v>127362721</v>
       </c>
       <c r="B76" t="n">
         <v>98443</v>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9062,10 +9062,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>474704</v>
+        <v>474740</v>
       </c>
       <c r="R76" t="n">
-        <v>6848745</v>
+        <v>6848725</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9134,7 +9134,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127363816</v>
+        <v>127362532</v>
       </c>
       <c r="B77" t="n">
         <v>98443</v>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9173,10 +9173,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>474651</v>
+        <v>474704</v>
       </c>
       <c r="R77" t="n">
-        <v>6848722</v>
+        <v>6848745</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -5265,7 +5265,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127362966</v>
+        <v>127362304</v>
       </c>
       <c r="B42" t="n">
         <v>98443</v>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5309,13 +5309,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474752</v>
+        <v>474663</v>
       </c>
       <c r="R42" t="n">
-        <v>6848680</v>
+        <v>6848747</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5342,19 +5342,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5369,19 +5359,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127362304</v>
+        <v>127362966</v>
       </c>
       <c r="B43" t="n">
         <v>98443</v>
@@ -5411,12 +5401,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5425,13 +5415,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474663</v>
+        <v>474752</v>
       </c>
       <c r="R43" t="n">
-        <v>6848747</v>
+        <v>6848680</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5458,9 +5448,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5475,12 +5475,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5586,12 +5586,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5697,12 +5697,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5803,12 +5803,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5909,12 +5909,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6015,12 +6015,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6121,12 +6121,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6341,7 +6341,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127386307</v>
+        <v>127362672</v>
       </c>
       <c r="B52" t="n">
         <v>98443</v>
@@ -6371,26 +6371,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474736</v>
+        <v>474728</v>
       </c>
       <c r="R52" t="n">
-        <v>6848669</v>
+        <v>6848726</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6417,37 +6418,46 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127362672</v>
+        <v>127386307</v>
       </c>
       <c r="B53" t="n">
         <v>98443</v>
@@ -6477,27 +6487,26 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kontoret, Kontoret, Hjd</t>
+          <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474728</v>
+        <v>474736</v>
       </c>
       <c r="R53" t="n">
-        <v>6848726</v>
+        <v>6848669</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6524,101 +6533,78 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127363005</v>
+        <v>127402796</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474656</v>
+        <v>474724</v>
       </c>
       <c r="R54" t="n">
-        <v>6848946</v>
+        <v>6848762</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6642,22 +6628,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6672,60 +6648,74 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127402796</v>
+        <v>127363005</v>
       </c>
       <c r="B55" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474724</v>
+        <v>474656</v>
       </c>
       <c r="R55" t="n">
-        <v>6848762</v>
+        <v>6848946</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6749,12 +6739,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6769,12 +6769,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6878,45 +6878,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127362687</v>
+        <v>127361760</v>
       </c>
       <c r="B57" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474755</v>
+        <v>474655</v>
       </c>
       <c r="R57" t="n">
-        <v>6848852</v>
+        <v>6848869</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6948,7 +6953,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6958,7 +6963,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6985,7 +6990,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127362535</v>
+        <v>127362687</v>
       </c>
       <c r="B58" t="n">
         <v>98443</v>
@@ -7013,31 +7018,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474796</v>
+        <v>474755</v>
       </c>
       <c r="R58" t="n">
-        <v>6848733</v>
+        <v>6848852</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7069,7 +7060,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7079,7 +7070,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7106,38 +7097,47 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127361760</v>
+        <v>127362535</v>
       </c>
       <c r="B59" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474655</v>
+        <v>474796</v>
       </c>
       <c r="R59" t="n">
-        <v>6848869</v>
+        <v>6848733</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7218,48 +7218,57 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127361676</v>
+        <v>127361806</v>
       </c>
       <c r="B60" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474659</v>
+        <v>474668</v>
       </c>
       <c r="R60" t="n">
-        <v>6848942</v>
+        <v>6848864</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7288,7 +7297,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7298,7 +7307,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7313,19 +7322,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127361806</v>
+        <v>127362598</v>
       </c>
       <c r="B61" t="n">
         <v>98443</v>
@@ -7355,12 +7364,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7369,10 +7373,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474668</v>
+        <v>474703</v>
       </c>
       <c r="R61" t="n">
-        <v>6848864</v>
+        <v>6848747</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7404,7 +7408,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7414,7 +7418,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7434,59 +7438,55 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127362598</v>
+        <v>127361676</v>
       </c>
       <c r="B62" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>474703</v>
+        <v>474659</v>
       </c>
       <c r="R62" t="n">
-        <v>6848747</v>
+        <v>6848942</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7540,12 +7540,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7663,48 +7663,57 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127362191</v>
+        <v>127363437</v>
       </c>
       <c r="B64" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474687</v>
+        <v>474725</v>
       </c>
       <c r="R64" t="n">
-        <v>6848753</v>
+        <v>6848676</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7733,7 +7742,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7743,7 +7752,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7758,69 +7767,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127363437</v>
+        <v>127362191</v>
       </c>
       <c r="B65" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474725</v>
+        <v>474687</v>
       </c>
       <c r="R65" t="n">
-        <v>6848676</v>
+        <v>6848753</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7874,49 +7874,50 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127361820</v>
+        <v>127361703</v>
       </c>
       <c r="B66" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7925,13 +7926,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474667</v>
+        <v>474655</v>
       </c>
       <c r="R66" t="n">
-        <v>6848863</v>
+        <v>6848935</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7960,7 +7961,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7970,7 +7971,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7985,50 +7986,49 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127361703</v>
+        <v>127361820</v>
       </c>
       <c r="B67" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474655</v>
+        <v>474667</v>
       </c>
       <c r="R67" t="n">
-        <v>6848935</v>
+        <v>6848863</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8097,12 +8097,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8225,7 +8225,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127362521</v>
+        <v>127363059</v>
       </c>
       <c r="B69" t="n">
         <v>98443</v>
@@ -8255,12 +8255,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8269,10 +8264,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474703</v>
+        <v>474726</v>
       </c>
       <c r="R69" t="n">
-        <v>6848742</v>
+        <v>6848721</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8304,7 +8299,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8314,7 +8309,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8334,14 +8329,14 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127362960</v>
+        <v>127362521</v>
       </c>
       <c r="B70" t="n">
         <v>98443</v>
@@ -8371,12 +8366,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -8390,13 +8380,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474647</v>
+        <v>474703</v>
       </c>
       <c r="R70" t="n">
-        <v>6848955</v>
+        <v>6848742</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8425,7 +8415,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8435,7 +8425,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8450,19 +8440,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127363059</v>
+        <v>127362960</v>
       </c>
       <c r="B71" t="n">
         <v>98443</v>
@@ -8492,7 +8482,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8501,13 +8501,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474726</v>
+        <v>474647</v>
       </c>
       <c r="R71" t="n">
-        <v>6848721</v>
+        <v>6848955</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8561,12 +8561,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9699,7 +9699,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127362816</v>
+        <v>127402462</v>
       </c>
       <c r="B82" t="n">
         <v>98443</v>
@@ -9727,21 +9727,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>474739</v>
+        <v>474630</v>
       </c>
       <c r="R82" t="n">
-        <v>6848699</v>
+        <v>6848862</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9768,22 +9764,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9798,19 +9784,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger , Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger , Erik Christiansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127363338</v>
+        <v>127362816</v>
       </c>
       <c r="B83" t="n">
         <v>98443</v>
@@ -9840,12 +9826,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9854,10 +9835,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>474730</v>
+        <v>474739</v>
       </c>
       <c r="R83" t="n">
-        <v>6848680</v>
+        <v>6848699</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9889,7 +9870,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9899,7 +9880,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9919,14 +9900,14 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127402462</v>
+        <v>127363338</v>
       </c>
       <c r="B84" t="n">
         <v>98443</v>
@@ -9954,17 +9935,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>474630</v>
+        <v>474730</v>
       </c>
       <c r="R84" t="n">
-        <v>6848862</v>
+        <v>6848680</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9991,12 +9981,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10011,12 +10011,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -6660,62 +6660,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127363005</v>
+        <v>127402478</v>
       </c>
       <c r="B55" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474656</v>
+        <v>474626</v>
       </c>
       <c r="R55" t="n">
-        <v>6848946</v>
+        <v>6848851</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6739,22 +6725,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6769,60 +6745,74 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127402478</v>
+        <v>127363005</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474626</v>
+        <v>474656</v>
       </c>
       <c r="R56" t="n">
-        <v>6848851</v>
+        <v>6848946</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6846,12 +6836,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,12 +6866,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -8225,7 +8225,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127363059</v>
+        <v>127362521</v>
       </c>
       <c r="B69" t="n">
         <v>98443</v>
@@ -8255,7 +8255,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8264,10 +8269,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474726</v>
+        <v>474703</v>
       </c>
       <c r="R69" t="n">
-        <v>6848721</v>
+        <v>6848742</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8299,7 +8304,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8309,7 +8314,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8329,14 +8334,14 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127362521</v>
+        <v>127363059</v>
       </c>
       <c r="B70" t="n">
         <v>98443</v>
@@ -8366,12 +8371,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8380,10 +8380,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474703</v>
+        <v>474726</v>
       </c>
       <c r="R70" t="n">
-        <v>6848742</v>
+        <v>6848721</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8415,7 +8415,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -8341,7 +8341,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127363059</v>
+        <v>127362960</v>
       </c>
       <c r="B70" t="n">
         <v>98443</v>
@@ -8371,7 +8371,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8380,13 +8390,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474726</v>
+        <v>474647</v>
       </c>
       <c r="R70" t="n">
-        <v>6848721</v>
+        <v>6848955</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8415,7 +8425,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8425,7 +8435,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8440,19 +8450,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127362960</v>
+        <v>127363059</v>
       </c>
       <c r="B71" t="n">
         <v>98443</v>
@@ -8482,17 +8492,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8501,13 +8501,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474647</v>
+        <v>474726</v>
       </c>
       <c r="R71" t="n">
-        <v>6848955</v>
+        <v>6848721</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8561,12 +8561,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -5268,7 +5268,7 @@
         <v>127362304</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>127362966</v>
       </c>
       <c r="B43" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>127362991</v>
       </c>
       <c r="B44" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>127362853</v>
       </c>
       <c r="B45" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>127362917</v>
       </c>
       <c r="B46" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127363562</v>
       </c>
       <c r="B47" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>127362771</v>
       </c>
       <c r="B48" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>127362641</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127363457</v>
+        <v>127402375</v>
       </c>
       <c r="B50" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6161,24 +6161,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474724</v>
+        <v>474605</v>
       </c>
       <c r="R50" t="n">
-        <v>6848681</v>
+        <v>6848875</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6202,22 +6198,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6232,22 +6218,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127402375</v>
+        <v>127363457</v>
       </c>
       <c r="B51" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6272,20 +6258,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474605</v>
+        <v>474724</v>
       </c>
       <c r="R51" t="n">
-        <v>6848875</v>
+        <v>6848681</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6309,12 +6299,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6329,12 +6329,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6344,7 +6344,7 @@
         <v>127362672</v>
       </c>
       <c r="B52" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>127386307</v>
       </c>
       <c r="B53" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>127402796</v>
       </c>
       <c r="B54" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>127402478</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>127363005</v>
       </c>
       <c r="B56" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>127361760</v>
       </c>
       <c r="B57" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>127362687</v>
       </c>
       <c r="B58" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>127362535</v>
       </c>
       <c r="B59" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7218,57 +7218,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127361806</v>
+        <v>127361676</v>
       </c>
       <c r="B60" t="n">
-        <v>98443</v>
+        <v>79050</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474668</v>
+        <v>474659</v>
       </c>
       <c r="R60" t="n">
-        <v>6848864</v>
+        <v>6848942</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7297,7 +7288,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7307,7 +7298,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7322,22 +7313,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127362598</v>
+        <v>127361806</v>
       </c>
       <c r="B61" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7364,7 +7355,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7373,10 +7369,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474703</v>
+        <v>474668</v>
       </c>
       <c r="R61" t="n">
-        <v>6848747</v>
+        <v>6848864</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7408,7 +7404,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7418,7 +7414,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7445,48 +7441,52 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127361676</v>
+        <v>127362598</v>
       </c>
       <c r="B62" t="n">
-        <v>79046</v>
+        <v>98447</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>474659</v>
+        <v>474703</v>
       </c>
       <c r="R62" t="n">
-        <v>6848942</v>
+        <v>6848747</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7540,12 +7540,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7555,7 +7555,7 @@
         <v>127363240</v>
       </c>
       <c r="B63" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7663,57 +7663,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127363437</v>
+        <v>127362191</v>
       </c>
       <c r="B64" t="n">
-        <v>98443</v>
+        <v>91330</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474725</v>
+        <v>474687</v>
       </c>
       <c r="R64" t="n">
-        <v>6848676</v>
+        <v>6848753</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7742,7 +7733,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7752,7 +7743,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7767,60 +7758,69 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127362191</v>
+        <v>127363437</v>
       </c>
       <c r="B65" t="n">
-        <v>91326</v>
+        <v>98447</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474687</v>
+        <v>474725</v>
       </c>
       <c r="R65" t="n">
-        <v>6848753</v>
+        <v>6848676</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7874,12 +7874,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7889,7 +7889,7 @@
         <v>127361703</v>
       </c>
       <c r="B66" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>127361820</v>
       </c>
       <c r="B67" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>127362891</v>
       </c>
       <c r="B68" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>127362521</v>
       </c>
       <c r="B69" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8341,10 +8341,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127362960</v>
+        <v>127363059</v>
       </c>
       <c r="B70" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8371,17 +8371,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8390,13 +8380,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474647</v>
+        <v>474726</v>
       </c>
       <c r="R70" t="n">
-        <v>6848955</v>
+        <v>6848721</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8425,7 +8415,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8435,7 +8425,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8450,22 +8440,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127363059</v>
+        <v>127362960</v>
       </c>
       <c r="B71" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8492,7 +8482,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8501,13 +8501,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474726</v>
+        <v>474647</v>
       </c>
       <c r="R71" t="n">
-        <v>6848721</v>
+        <v>6848955</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8561,12 +8561,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8576,7 +8576,7 @@
         <v>127362832</v>
       </c>
       <c r="B72" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>127362075</v>
       </c>
       <c r="B73" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>127363018</v>
       </c>
       <c r="B74" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>127363816</v>
       </c>
       <c r="B75" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>127362721</v>
       </c>
       <c r="B76" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>127362532</v>
       </c>
       <c r="B77" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>127362954</v>
       </c>
       <c r="B78" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>127363287</v>
       </c>
       <c r="B79" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>127362906</v>
       </c>
       <c r="B80" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>127363073</v>
       </c>
       <c r="B81" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>127402462</v>
       </c>
       <c r="B82" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>127362816</v>
       </c>
       <c r="B83" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>127363338</v>
       </c>
       <c r="B84" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -6563,48 +6563,62 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127402796</v>
+        <v>127363005</v>
       </c>
       <c r="B54" t="n">
-        <v>79050</v>
+        <v>98447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474724</v>
+        <v>474656</v>
       </c>
       <c r="R54" t="n">
-        <v>6848762</v>
+        <v>6848946</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6628,12 +6642,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6648,12 +6672,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6757,62 +6781,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127363005</v>
+        <v>127402796</v>
       </c>
       <c r="B56" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474656</v>
+        <v>474724</v>
       </c>
       <c r="R56" t="n">
-        <v>6848946</v>
+        <v>6848762</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6836,22 +6846,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,12 +6866,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7218,48 +7218,57 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127361676</v>
+        <v>127361806</v>
       </c>
       <c r="B60" t="n">
-        <v>79050</v>
+        <v>98447</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474659</v>
+        <v>474668</v>
       </c>
       <c r="R60" t="n">
-        <v>6848942</v>
+        <v>6848864</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7288,7 +7297,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7298,7 +7307,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7313,19 +7322,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127361806</v>
+        <v>127362598</v>
       </c>
       <c r="B61" t="n">
         <v>98447</v>
@@ -7355,12 +7364,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7369,10 +7373,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474668</v>
+        <v>474703</v>
       </c>
       <c r="R61" t="n">
-        <v>6848864</v>
+        <v>6848747</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7404,7 +7408,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7414,7 +7418,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7441,52 +7445,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127362598</v>
+        <v>127361676</v>
       </c>
       <c r="B62" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>474703</v>
+        <v>474659</v>
       </c>
       <c r="R62" t="n">
-        <v>6848747</v>
+        <v>6848942</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7540,12 +7540,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -7218,57 +7218,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127361806</v>
+        <v>127361676</v>
       </c>
       <c r="B60" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474668</v>
+        <v>474659</v>
       </c>
       <c r="R60" t="n">
-        <v>6848864</v>
+        <v>6848942</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7297,7 +7288,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7307,7 +7298,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7322,19 +7313,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127362598</v>
+        <v>127361806</v>
       </c>
       <c r="B61" t="n">
         <v>98447</v>
@@ -7364,7 +7355,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7373,10 +7369,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474703</v>
+        <v>474668</v>
       </c>
       <c r="R61" t="n">
-        <v>6848747</v>
+        <v>6848864</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7408,7 +7404,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7418,7 +7414,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7445,48 +7441,52 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127361676</v>
+        <v>127362598</v>
       </c>
       <c r="B62" t="n">
-        <v>79050</v>
+        <v>98447</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>474659</v>
+        <v>474703</v>
       </c>
       <c r="R62" t="n">
-        <v>6848942</v>
+        <v>6848747</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7540,12 +7540,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -6563,62 +6563,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127363005</v>
+        <v>127402796</v>
       </c>
       <c r="B54" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474656</v>
+        <v>474724</v>
       </c>
       <c r="R54" t="n">
-        <v>6848946</v>
+        <v>6848762</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6642,22 +6628,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6672,12 +6648,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6781,48 +6757,62 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127402796</v>
+        <v>127363005</v>
       </c>
       <c r="B56" t="n">
-        <v>79050</v>
+        <v>98447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474724</v>
+        <v>474656</v>
       </c>
       <c r="R56" t="n">
-        <v>6848762</v>
+        <v>6848946</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6846,12 +6836,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,12 +6866,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -5268,7 +5268,7 @@
         <v>127362304</v>
       </c>
       <c r="B42" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>127362966</v>
       </c>
       <c r="B43" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>127362991</v>
       </c>
       <c r="B44" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>127362853</v>
       </c>
       <c r="B45" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>127362917</v>
       </c>
       <c r="B46" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127363562</v>
       </c>
       <c r="B47" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>127362771</v>
       </c>
       <c r="B48" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>127362641</v>
       </c>
       <c r="B49" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>127402375</v>
       </c>
       <c r="B50" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>127363457</v>
       </c>
       <c r="B51" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>127362672</v>
       </c>
       <c r="B52" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>127386307</v>
       </c>
       <c r="B53" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6563,48 +6563,62 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127402796</v>
+        <v>127363005</v>
       </c>
       <c r="B54" t="n">
-        <v>79050</v>
+        <v>98448</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474724</v>
+        <v>474656</v>
       </c>
       <c r="R54" t="n">
-        <v>6848762</v>
+        <v>6848946</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6628,12 +6642,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6648,12 +6672,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6757,62 +6781,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127363005</v>
+        <v>127402796</v>
       </c>
       <c r="B56" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474656</v>
+        <v>474724</v>
       </c>
       <c r="R56" t="n">
-        <v>6848946</v>
+        <v>6848762</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6836,22 +6846,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,62 +6866,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127361760</v>
+        <v>127362687</v>
       </c>
       <c r="B57" t="n">
-        <v>57661</v>
+        <v>98448</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474655</v>
+        <v>474755</v>
       </c>
       <c r="R57" t="n">
-        <v>6848869</v>
+        <v>6848852</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6953,7 +6948,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6963,7 +6958,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6990,10 +6985,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127362687</v>
+        <v>127362535</v>
       </c>
       <c r="B58" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7018,17 +7013,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474755</v>
+        <v>474796</v>
       </c>
       <c r="R58" t="n">
-        <v>6848852</v>
+        <v>6848733</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7060,7 +7069,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7070,7 +7079,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7097,47 +7106,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127362535</v>
+        <v>127361760</v>
       </c>
       <c r="B59" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474796</v>
+        <v>474655</v>
       </c>
       <c r="R59" t="n">
-        <v>6848733</v>
+        <v>6848869</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7328,7 +7328,7 @@
         <v>127361806</v>
       </c>
       <c r="B61" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>127362598</v>
       </c>
       <c r="B62" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>127363240</v>
       </c>
       <c r="B63" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>127363437</v>
       </c>
       <c r="B65" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>127361820</v>
       </c>
       <c r="B67" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>127362891</v>
       </c>
       <c r="B68" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>127362521</v>
       </c>
       <c r="B69" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>127363059</v>
       </c>
       <c r="B70" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>127362960</v>
       </c>
       <c r="B71" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>127362832</v>
       </c>
       <c r="B72" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>127363018</v>
       </c>
       <c r="B74" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8912,10 +8912,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127363816</v>
+        <v>127362721</v>
       </c>
       <c r="B75" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>474651</v>
+        <v>474740</v>
       </c>
       <c r="R75" t="n">
-        <v>6848722</v>
+        <v>6848725</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9016,17 +9016,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127362721</v>
+        <v>127362532</v>
       </c>
       <c r="B76" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9062,10 +9062,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>474740</v>
+        <v>474704</v>
       </c>
       <c r="R76" t="n">
-        <v>6848725</v>
+        <v>6848745</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9134,10 +9134,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127362532</v>
+        <v>127363816</v>
       </c>
       <c r="B77" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9173,10 +9173,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>474704</v>
+        <v>474651</v>
       </c>
       <c r="R77" t="n">
-        <v>6848745</v>
+        <v>6848722</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9248,7 +9248,7 @@
         <v>127362954</v>
       </c>
       <c r="B78" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>127363287</v>
       </c>
       <c r="B79" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>127362906</v>
       </c>
       <c r="B80" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>127363073</v>
       </c>
       <c r="B81" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127402462</v>
+        <v>127362816</v>
       </c>
       <c r="B82" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9727,17 +9727,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>474630</v>
+        <v>474739</v>
       </c>
       <c r="R82" t="n">
-        <v>6848862</v>
+        <v>6848699</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9764,12 +9768,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9784,22 +9798,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127362816</v>
+        <v>127363338</v>
       </c>
       <c r="B83" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9826,7 +9840,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9835,10 +9854,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>474739</v>
+        <v>474730</v>
       </c>
       <c r="R83" t="n">
-        <v>6848699</v>
+        <v>6848680</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9870,7 +9889,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9880,7 +9899,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9900,17 +9919,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127363338</v>
+        <v>127402462</v>
       </c>
       <c r="B84" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9935,26 +9954,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>474730</v>
+        <v>474630</v>
       </c>
       <c r="R84" t="n">
-        <v>6848680</v>
+        <v>6848862</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9981,22 +9991,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10011,12 +10011,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -6133,7 +6133,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127402375</v>
+        <v>127363457</v>
       </c>
       <c r="B50" t="n">
         <v>98448</v>
@@ -6161,20 +6161,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474605</v>
+        <v>474724</v>
       </c>
       <c r="R50" t="n">
-        <v>6848875</v>
+        <v>6848681</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6198,12 +6202,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6218,19 +6232,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127363457</v>
+        <v>127402375</v>
       </c>
       <c r="B51" t="n">
         <v>98448</v>
@@ -6258,24 +6272,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474724</v>
+        <v>474605</v>
       </c>
       <c r="R51" t="n">
-        <v>6848681</v>
+        <v>6848875</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6299,22 +6309,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6329,12 +6329,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6563,62 +6563,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127363005</v>
+        <v>127402796</v>
       </c>
       <c r="B54" t="n">
-        <v>98448</v>
+        <v>79050</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474656</v>
+        <v>474724</v>
       </c>
       <c r="R54" t="n">
-        <v>6848946</v>
+        <v>6848762</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6642,22 +6628,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6672,12 +6648,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6781,48 +6757,62 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127402796</v>
+        <v>127363005</v>
       </c>
       <c r="B56" t="n">
-        <v>79050</v>
+        <v>98448</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474724</v>
+        <v>474656</v>
       </c>
       <c r="R56" t="n">
-        <v>6848762</v>
+        <v>6848946</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6846,12 +6836,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,12 +6866,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -8912,7 +8912,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127362721</v>
+        <v>127363816</v>
       </c>
       <c r="B75" t="n">
         <v>98448</v>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>474740</v>
+        <v>474651</v>
       </c>
       <c r="R75" t="n">
-        <v>6848725</v>
+        <v>6848722</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9016,14 +9016,14 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127362532</v>
+        <v>127362721</v>
       </c>
       <c r="B76" t="n">
         <v>98448</v>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9062,10 +9062,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>474704</v>
+        <v>474740</v>
       </c>
       <c r="R76" t="n">
-        <v>6848745</v>
+        <v>6848725</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9134,7 +9134,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127363816</v>
+        <v>127362532</v>
       </c>
       <c r="B77" t="n">
         <v>98448</v>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9173,10 +9173,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>474651</v>
+        <v>474704</v>
       </c>
       <c r="R77" t="n">
-        <v>6848722</v>
+        <v>6848745</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -5265,10 +5265,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127362304</v>
+        <v>127362966</v>
       </c>
       <c r="B42" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5309,13 +5309,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474663</v>
+        <v>474752</v>
       </c>
       <c r="R42" t="n">
-        <v>6848747</v>
+        <v>6848680</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5342,9 +5342,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5359,22 +5369,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127362966</v>
+        <v>127362304</v>
       </c>
       <c r="B43" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5401,12 +5411,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5415,13 +5425,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474752</v>
+        <v>474663</v>
       </c>
       <c r="R43" t="n">
-        <v>6848680</v>
+        <v>6848747</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5448,19 +5458,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5475,12 +5475,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5490,7 +5490,7 @@
         <v>127362991</v>
       </c>
       <c r="B44" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>127362853</v>
       </c>
       <c r="B45" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>127362917</v>
       </c>
       <c r="B46" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127363562</v>
       </c>
       <c r="B47" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>127362771</v>
       </c>
       <c r="B48" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>127362641</v>
       </c>
       <c r="B49" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127363457</v>
+        <v>127402375</v>
       </c>
       <c r="B50" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6161,24 +6161,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474724</v>
+        <v>474605</v>
       </c>
       <c r="R50" t="n">
-        <v>6848681</v>
+        <v>6848875</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6202,22 +6198,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6232,22 +6218,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127402375</v>
+        <v>127363457</v>
       </c>
       <c r="B51" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6272,20 +6258,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474605</v>
+        <v>474724</v>
       </c>
       <c r="R51" t="n">
-        <v>6848875</v>
+        <v>6848681</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6309,12 +6299,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6329,22 +6329,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127362672</v>
+        <v>127386307</v>
       </c>
       <c r="B52" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6371,27 +6371,26 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kontoret, Kontoret, Hjd</t>
+          <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474728</v>
+        <v>474736</v>
       </c>
       <c r="R52" t="n">
-        <v>6848726</v>
+        <v>6848669</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6418,49 +6417,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127386307</v>
+        <v>127362672</v>
       </c>
       <c r="B53" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6487,26 +6477,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474736</v>
+        <v>474728</v>
       </c>
       <c r="R53" t="n">
-        <v>6848669</v>
+        <v>6848726</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,40 +6524,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127402796</v>
+        <v>127402478</v>
       </c>
       <c r="B54" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6574,21 +6574,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6598,10 +6598,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474724</v>
+        <v>474626</v>
       </c>
       <c r="R54" t="n">
-        <v>6848762</v>
+        <v>6848851</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6660,10 +6660,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127402478</v>
+        <v>127402796</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6671,21 +6671,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6695,10 +6695,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474626</v>
+        <v>474724</v>
       </c>
       <c r="R55" t="n">
-        <v>6848851</v>
+        <v>6848762</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6760,7 +6760,7 @@
         <v>127363005</v>
       </c>
       <c r="B56" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6878,45 +6878,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127362687</v>
+        <v>127361760</v>
       </c>
       <c r="B57" t="n">
-        <v>98448</v>
+        <v>57663</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474755</v>
+        <v>474655</v>
       </c>
       <c r="R57" t="n">
-        <v>6848852</v>
+        <v>6848869</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6948,7 +6953,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6958,7 +6963,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6985,10 +6990,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127362535</v>
+        <v>127362687</v>
       </c>
       <c r="B58" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7013,31 +7018,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474796</v>
+        <v>474755</v>
       </c>
       <c r="R58" t="n">
-        <v>6848733</v>
+        <v>6848852</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7069,7 +7060,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7079,7 +7070,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7106,38 +7097,47 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127361760</v>
+        <v>127362535</v>
       </c>
       <c r="B59" t="n">
-        <v>57661</v>
+        <v>98450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474655</v>
+        <v>474796</v>
       </c>
       <c r="R59" t="n">
-        <v>6848869</v>
+        <v>6848733</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7221,7 +7221,7 @@
         <v>127361676</v>
       </c>
       <c r="B60" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>127361806</v>
       </c>
       <c r="B61" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>127362598</v>
       </c>
       <c r="B62" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>127363240</v>
       </c>
       <c r="B63" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>127362191</v>
       </c>
       <c r="B64" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>127363437</v>
       </c>
       <c r="B65" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>127361703</v>
       </c>
       <c r="B66" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127361820</v>
+        <v>127362891</v>
       </c>
       <c r="B67" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8028,7 +8028,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8037,10 +8042,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474667</v>
+        <v>474768</v>
       </c>
       <c r="R67" t="n">
-        <v>6848863</v>
+        <v>6848772</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8072,7 +8077,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8082,7 +8087,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8102,17 +8107,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127362891</v>
+        <v>127361820</v>
       </c>
       <c r="B68" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8139,12 +8144,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8153,10 +8153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474768</v>
+        <v>474667</v>
       </c>
       <c r="R68" t="n">
-        <v>6848772</v>
+        <v>6848863</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8228,7 +8228,7 @@
         <v>127362521</v>
       </c>
       <c r="B69" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>127363059</v>
       </c>
       <c r="B70" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>127362960</v>
       </c>
       <c r="B71" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>127362832</v>
       </c>
       <c r="B72" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>127362075</v>
       </c>
       <c r="B73" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>127363018</v>
       </c>
       <c r="B74" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8912,10 +8912,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127363816</v>
+        <v>127362532</v>
       </c>
       <c r="B75" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>474651</v>
+        <v>474704</v>
       </c>
       <c r="R75" t="n">
-        <v>6848722</v>
+        <v>6848745</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9026,7 +9026,7 @@
         <v>127362721</v>
       </c>
       <c r="B76" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9134,10 +9134,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127362532</v>
+        <v>127363816</v>
       </c>
       <c r="B77" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9173,10 +9173,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>474704</v>
+        <v>474651</v>
       </c>
       <c r="R77" t="n">
-        <v>6848745</v>
+        <v>6848722</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9248,7 +9248,7 @@
         <v>127362954</v>
       </c>
       <c r="B78" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>127363287</v>
       </c>
       <c r="B79" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>127362906</v>
       </c>
       <c r="B80" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>127363073</v>
       </c>
       <c r="B81" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127362816</v>
+        <v>127402462</v>
       </c>
       <c r="B82" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9727,21 +9727,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>474739</v>
+        <v>474630</v>
       </c>
       <c r="R82" t="n">
-        <v>6848699</v>
+        <v>6848862</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9768,22 +9764,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9798,22 +9784,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127363338</v>
+        <v>127362816</v>
       </c>
       <c r="B83" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9840,12 +9826,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9854,10 +9835,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>474730</v>
+        <v>474739</v>
       </c>
       <c r="R83" t="n">
-        <v>6848680</v>
+        <v>6848699</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9889,7 +9870,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9899,7 +9880,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9919,17 +9900,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127402462</v>
+        <v>127363338</v>
       </c>
       <c r="B84" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9954,17 +9935,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>474630</v>
+        <v>474730</v>
       </c>
       <c r="R84" t="n">
-        <v>6848862</v>
+        <v>6848680</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9991,12 +9981,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10011,12 +10011,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -5265,7 +5265,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127362966</v>
+        <v>127362304</v>
       </c>
       <c r="B42" t="n">
         <v>98450</v>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5309,13 +5309,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474752</v>
+        <v>474663</v>
       </c>
       <c r="R42" t="n">
-        <v>6848680</v>
+        <v>6848747</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5342,19 +5342,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5369,19 +5359,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127362304</v>
+        <v>127362966</v>
       </c>
       <c r="B43" t="n">
         <v>98450</v>
@@ -5411,12 +5401,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5425,13 +5415,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474663</v>
+        <v>474752</v>
       </c>
       <c r="R43" t="n">
-        <v>6848747</v>
+        <v>6848680</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5458,9 +5448,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5475,12 +5475,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6341,7 +6341,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127386307</v>
+        <v>127362672</v>
       </c>
       <c r="B52" t="n">
         <v>98450</v>
@@ -6371,26 +6371,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474736</v>
+        <v>474728</v>
       </c>
       <c r="R52" t="n">
-        <v>6848669</v>
+        <v>6848726</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6417,37 +6418,46 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127362672</v>
+        <v>127386307</v>
       </c>
       <c r="B53" t="n">
         <v>98450</v>
@@ -6477,27 +6487,26 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kontoret, Kontoret, Hjd</t>
+          <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474728</v>
+        <v>474736</v>
       </c>
       <c r="R53" t="n">
-        <v>6848726</v>
+        <v>6848669</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6524,49 +6533,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127402478</v>
+        <v>127402796</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6574,21 +6574,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6598,10 +6598,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474626</v>
+        <v>474724</v>
       </c>
       <c r="R54" t="n">
-        <v>6848851</v>
+        <v>6848762</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6660,10 +6660,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127402796</v>
+        <v>127402478</v>
       </c>
       <c r="B55" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6671,21 +6671,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6695,10 +6695,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474724</v>
+        <v>474626</v>
       </c>
       <c r="R55" t="n">
-        <v>6848762</v>
+        <v>6848851</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -7998,7 +7998,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127362891</v>
+        <v>127361820</v>
       </c>
       <c r="B67" t="n">
         <v>98450</v>
@@ -8028,12 +8028,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8042,10 +8037,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474768</v>
+        <v>474667</v>
       </c>
       <c r="R67" t="n">
-        <v>6848772</v>
+        <v>6848863</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8077,7 +8072,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8087,7 +8082,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8107,14 +8102,14 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127361820</v>
+        <v>127362891</v>
       </c>
       <c r="B68" t="n">
         <v>98450</v>
@@ -8144,7 +8139,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8153,10 +8153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474667</v>
+        <v>474768</v>
       </c>
       <c r="R68" t="n">
-        <v>6848863</v>
+        <v>6848772</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8912,7 +8912,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127362532</v>
+        <v>127363816</v>
       </c>
       <c r="B75" t="n">
         <v>98450</v>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>474704</v>
+        <v>474651</v>
       </c>
       <c r="R75" t="n">
-        <v>6848745</v>
+        <v>6848722</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9134,7 +9134,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127363816</v>
+        <v>127362532</v>
       </c>
       <c r="B77" t="n">
         <v>98450</v>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9173,10 +9173,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>474651</v>
+        <v>474704</v>
       </c>
       <c r="R77" t="n">
-        <v>6848722</v>
+        <v>6848745</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -7886,38 +7886,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127361703</v>
+        <v>127361820</v>
       </c>
       <c r="B66" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7926,13 +7925,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474655</v>
+        <v>474667</v>
       </c>
       <c r="R66" t="n">
-        <v>6848935</v>
+        <v>6848863</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7961,7 +7960,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7971,7 +7970,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7986,19 +7985,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127361820</v>
+        <v>127362891</v>
       </c>
       <c r="B67" t="n">
         <v>98450</v>
@@ -8028,7 +8027,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8037,10 +8041,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474667</v>
+        <v>474768</v>
       </c>
       <c r="R67" t="n">
-        <v>6848863</v>
+        <v>6848772</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8072,7 +8076,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8082,7 +8086,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8102,49 +8106,45 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127362891</v>
+        <v>127361703</v>
       </c>
       <c r="B68" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8153,13 +8153,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474768</v>
+        <v>474655</v>
       </c>
       <c r="R68" t="n">
-        <v>6848772</v>
+        <v>6848935</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8213,12 +8213,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -6341,7 +6341,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127362672</v>
+        <v>127386307</v>
       </c>
       <c r="B52" t="n">
         <v>98450</v>
@@ -6371,27 +6371,26 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kontoret, Kontoret, Hjd</t>
+          <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474728</v>
+        <v>474736</v>
       </c>
       <c r="R52" t="n">
-        <v>6848726</v>
+        <v>6848669</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6418,46 +6417,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127386307</v>
+        <v>127362672</v>
       </c>
       <c r="B53" t="n">
         <v>98450</v>
@@ -6487,26 +6477,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474736</v>
+        <v>474728</v>
       </c>
       <c r="R53" t="n">
-        <v>6848669</v>
+        <v>6848726</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,30 +6524,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6878,50 +6878,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127361760</v>
+        <v>127362687</v>
       </c>
       <c r="B57" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474655</v>
+        <v>474755</v>
       </c>
       <c r="R57" t="n">
-        <v>6848869</v>
+        <v>6848852</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6953,7 +6948,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6963,7 +6958,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6990,45 +6985,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127362687</v>
+        <v>127361760</v>
       </c>
       <c r="B58" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474755</v>
+        <v>474655</v>
       </c>
       <c r="R58" t="n">
-        <v>6848852</v>
+        <v>6848869</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7886,37 +7886,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127361820</v>
+        <v>127361703</v>
       </c>
       <c r="B66" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7925,13 +7926,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474667</v>
+        <v>474655</v>
       </c>
       <c r="R66" t="n">
-        <v>6848863</v>
+        <v>6848935</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7960,7 +7961,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7970,7 +7971,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7985,19 +7986,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127362891</v>
+        <v>127361820</v>
       </c>
       <c r="B67" t="n">
         <v>98450</v>
@@ -8027,12 +8028,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8041,10 +8037,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474768</v>
+        <v>474667</v>
       </c>
       <c r="R67" t="n">
-        <v>6848772</v>
+        <v>6848863</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8076,7 +8072,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8086,7 +8082,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8106,45 +8102,49 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127361703</v>
+        <v>127362891</v>
       </c>
       <c r="B68" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8153,13 +8153,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474655</v>
+        <v>474768</v>
       </c>
       <c r="R68" t="n">
-        <v>6848935</v>
+        <v>6848772</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8213,19 +8213,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127362521</v>
+        <v>127362960</v>
       </c>
       <c r="B69" t="n">
         <v>98450</v>
@@ -8255,7 +8255,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -8269,13 +8274,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474703</v>
+        <v>474647</v>
       </c>
       <c r="R69" t="n">
-        <v>6848742</v>
+        <v>6848955</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8304,7 +8309,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8314,7 +8319,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8329,19 +8334,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127363059</v>
+        <v>127362521</v>
       </c>
       <c r="B70" t="n">
         <v>98450</v>
@@ -8371,7 +8376,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8380,10 +8390,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474726</v>
+        <v>474703</v>
       </c>
       <c r="R70" t="n">
-        <v>6848721</v>
+        <v>6848742</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8415,7 +8425,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8425,7 +8435,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8445,14 +8455,14 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127362960</v>
+        <v>127363059</v>
       </c>
       <c r="B71" t="n">
         <v>98450</v>
@@ -8482,17 +8492,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8501,13 +8501,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474647</v>
+        <v>474726</v>
       </c>
       <c r="R71" t="n">
-        <v>6848955</v>
+        <v>6848721</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8561,12 +8561,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -5268,7 +5268,7 @@
         <v>127362304</v>
       </c>
       <c r="B42" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>127362966</v>
       </c>
       <c r="B43" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>127362991</v>
       </c>
       <c r="B44" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>127362853</v>
       </c>
       <c r="B45" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>127362917</v>
       </c>
       <c r="B46" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127363562</v>
       </c>
       <c r="B47" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127362771</v>
+        <v>127362641</v>
       </c>
       <c r="B48" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474749</v>
+        <v>474710</v>
       </c>
       <c r="R48" t="n">
-        <v>6848712</v>
+        <v>6848736</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6027,10 +6027,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127362641</v>
+        <v>127362771</v>
       </c>
       <c r="B49" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474710</v>
+        <v>474749</v>
       </c>
       <c r="R49" t="n">
-        <v>6848736</v>
+        <v>6848712</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6136,7 +6136,7 @@
         <v>127402375</v>
       </c>
       <c r="B50" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>127363457</v>
       </c>
       <c r="B51" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>127386307</v>
       </c>
       <c r="B52" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>127362672</v>
       </c>
       <c r="B53" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6563,48 +6563,62 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127402796</v>
+        <v>127363005</v>
       </c>
       <c r="B54" t="n">
-        <v>79052</v>
+        <v>98456</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474724</v>
+        <v>474656</v>
       </c>
       <c r="R54" t="n">
-        <v>6848762</v>
+        <v>6848946</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6628,12 +6642,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6648,22 +6672,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127402478</v>
+        <v>127402796</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6671,21 +6695,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6695,10 +6719,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474626</v>
+        <v>474724</v>
       </c>
       <c r="R55" t="n">
-        <v>6848851</v>
+        <v>6848762</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6757,62 +6781,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127363005</v>
+        <v>127402478</v>
       </c>
       <c r="B56" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474656</v>
+        <v>474626</v>
       </c>
       <c r="R56" t="n">
-        <v>6848946</v>
+        <v>6848851</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6836,22 +6846,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,57 +6866,62 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127362687</v>
+        <v>127361760</v>
       </c>
       <c r="B57" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474755</v>
+        <v>474655</v>
       </c>
       <c r="R57" t="n">
-        <v>6848852</v>
+        <v>6848869</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6948,7 +6953,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6958,7 +6963,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6985,38 +6990,47 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127361760</v>
+        <v>127362535</v>
       </c>
       <c r="B58" t="n">
-        <v>57663</v>
+        <v>98456</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7025,10 +7039,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474655</v>
+        <v>474796</v>
       </c>
       <c r="R58" t="n">
-        <v>6848869</v>
+        <v>6848733</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7060,7 +7074,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7070,7 +7084,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7097,10 +7111,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127362535</v>
+        <v>127362687</v>
       </c>
       <c r="B59" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7125,31 +7139,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474796</v>
+        <v>474755</v>
       </c>
       <c r="R59" t="n">
-        <v>6848733</v>
+        <v>6848852</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7328,7 +7328,7 @@
         <v>127361806</v>
       </c>
       <c r="B61" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>127362598</v>
       </c>
       <c r="B62" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>127363240</v>
       </c>
       <c r="B63" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>127362191</v>
       </c>
       <c r="B64" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>127363437</v>
       </c>
       <c r="B65" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127361820</v>
+        <v>127362891</v>
       </c>
       <c r="B67" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8028,7 +8028,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8037,10 +8042,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474667</v>
+        <v>474768</v>
       </c>
       <c r="R67" t="n">
-        <v>6848863</v>
+        <v>6848772</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8072,7 +8077,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8082,7 +8087,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8102,17 +8107,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127362891</v>
+        <v>127361820</v>
       </c>
       <c r="B68" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8139,12 +8144,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8153,10 +8153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474768</v>
+        <v>474667</v>
       </c>
       <c r="R68" t="n">
-        <v>6848772</v>
+        <v>6848863</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8228,7 +8228,7 @@
         <v>127362960</v>
       </c>
       <c r="B69" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>127362521</v>
       </c>
       <c r="B70" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>127363059</v>
       </c>
       <c r="B71" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>127362832</v>
       </c>
       <c r="B72" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>127362075</v>
       </c>
       <c r="B73" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>127363018</v>
       </c>
       <c r="B74" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8912,10 +8912,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127363816</v>
+        <v>127362532</v>
       </c>
       <c r="B75" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>474651</v>
+        <v>474704</v>
       </c>
       <c r="R75" t="n">
-        <v>6848722</v>
+        <v>6848745</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9026,7 +9026,7 @@
         <v>127362721</v>
       </c>
       <c r="B76" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9134,10 +9134,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127362532</v>
+        <v>127363816</v>
       </c>
       <c r="B77" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9173,10 +9173,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>474704</v>
+        <v>474651</v>
       </c>
       <c r="R77" t="n">
-        <v>6848745</v>
+        <v>6848722</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9248,7 +9248,7 @@
         <v>127362954</v>
       </c>
       <c r="B78" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>127363287</v>
       </c>
       <c r="B79" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>127362906</v>
       </c>
       <c r="B80" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>127363073</v>
       </c>
       <c r="B81" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127402462</v>
+        <v>127362816</v>
       </c>
       <c r="B82" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9727,17 +9727,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>474630</v>
+        <v>474739</v>
       </c>
       <c r="R82" t="n">
-        <v>6848862</v>
+        <v>6848699</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9764,12 +9768,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9784,22 +9798,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127362816</v>
+        <v>127363338</v>
       </c>
       <c r="B83" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9826,7 +9840,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9835,10 +9854,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>474739</v>
+        <v>474730</v>
       </c>
       <c r="R83" t="n">
-        <v>6848699</v>
+        <v>6848680</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9870,7 +9889,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9880,7 +9899,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9900,17 +9919,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127363338</v>
+        <v>127402462</v>
       </c>
       <c r="B84" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9935,26 +9954,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>474730</v>
+        <v>474630</v>
       </c>
       <c r="R84" t="n">
-        <v>6848680</v>
+        <v>6848862</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9981,22 +9991,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10011,12 +10011,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -5268,7 +5268,7 @@
         <v>127362304</v>
       </c>
       <c r="B42" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>127362966</v>
       </c>
       <c r="B43" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>127362991</v>
       </c>
       <c r="B44" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>127362853</v>
       </c>
       <c r="B45" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>127362917</v>
       </c>
       <c r="B46" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127363562</v>
       </c>
       <c r="B47" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127362641</v>
+        <v>127362771</v>
       </c>
       <c r="B48" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474710</v>
+        <v>474749</v>
       </c>
       <c r="R48" t="n">
-        <v>6848736</v>
+        <v>6848712</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6027,10 +6027,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127362771</v>
+        <v>127362641</v>
       </c>
       <c r="B49" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474749</v>
+        <v>474710</v>
       </c>
       <c r="R49" t="n">
-        <v>6848712</v>
+        <v>6848736</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6136,7 +6136,7 @@
         <v>127402375</v>
       </c>
       <c r="B50" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>127363457</v>
       </c>
       <c r="B51" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6341,10 +6341,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127386307</v>
+        <v>127362672</v>
       </c>
       <c r="B52" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6371,26 +6371,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474736</v>
+        <v>474728</v>
       </c>
       <c r="R52" t="n">
-        <v>6848669</v>
+        <v>6848726</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6417,40 +6418,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127362672</v>
+        <v>127386307</v>
       </c>
       <c r="B53" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6477,27 +6487,26 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kontoret, Kontoret, Hjd</t>
+          <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474728</v>
+        <v>474736</v>
       </c>
       <c r="R53" t="n">
-        <v>6848726</v>
+        <v>6848669</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6524,39 +6533,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
         <v>127363005</v>
       </c>
       <c r="B54" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>127402796</v>
       </c>
       <c r="B55" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>127402478</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6878,50 +6878,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127361760</v>
+        <v>127362687</v>
       </c>
       <c r="B57" t="n">
-        <v>57663</v>
+        <v>98459</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474655</v>
+        <v>474755</v>
       </c>
       <c r="R57" t="n">
-        <v>6848869</v>
+        <v>6848852</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6953,7 +6948,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6963,7 +6958,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6993,7 +6988,7 @@
         <v>127362535</v>
       </c>
       <c r="B58" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7111,45 +7106,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127362687</v>
+        <v>127361760</v>
       </c>
       <c r="B59" t="n">
-        <v>98456</v>
+        <v>57666</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474755</v>
+        <v>474655</v>
       </c>
       <c r="R59" t="n">
-        <v>6848852</v>
+        <v>6848869</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7221,7 +7221,7 @@
         <v>127361676</v>
       </c>
       <c r="B60" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>127361806</v>
       </c>
       <c r="B61" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>127362598</v>
       </c>
       <c r="B62" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>127363240</v>
       </c>
       <c r="B63" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>127362191</v>
       </c>
       <c r="B64" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>127363437</v>
       </c>
       <c r="B65" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>127361703</v>
       </c>
       <c r="B66" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127362891</v>
+        <v>127361820</v>
       </c>
       <c r="B67" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8028,12 +8028,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8042,10 +8037,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474768</v>
+        <v>474667</v>
       </c>
       <c r="R67" t="n">
-        <v>6848772</v>
+        <v>6848863</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8077,7 +8072,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8087,7 +8082,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8107,17 +8102,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127361820</v>
+        <v>127362891</v>
       </c>
       <c r="B68" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8144,7 +8139,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8153,10 +8153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474667</v>
+        <v>474768</v>
       </c>
       <c r="R68" t="n">
-        <v>6848863</v>
+        <v>6848772</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127362960</v>
+        <v>127362521</v>
       </c>
       <c r="B69" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8255,12 +8255,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -8274,13 +8269,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474647</v>
+        <v>474703</v>
       </c>
       <c r="R69" t="n">
-        <v>6848955</v>
+        <v>6848742</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8309,7 +8304,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8319,7 +8314,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8334,22 +8329,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127362521</v>
+        <v>127363059</v>
       </c>
       <c r="B70" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8376,12 +8371,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8390,10 +8380,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474703</v>
+        <v>474726</v>
       </c>
       <c r="R70" t="n">
-        <v>6848742</v>
+        <v>6848721</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8425,7 +8415,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8435,7 +8425,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8455,17 +8445,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127363059</v>
+        <v>127362960</v>
       </c>
       <c r="B71" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8492,7 +8482,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8501,13 +8501,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474726</v>
+        <v>474647</v>
       </c>
       <c r="R71" t="n">
-        <v>6848721</v>
+        <v>6848955</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8561,12 +8561,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8576,7 +8576,7 @@
         <v>127362832</v>
       </c>
       <c r="B72" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>127362075</v>
       </c>
       <c r="B73" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>127363018</v>
       </c>
       <c r="B74" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8912,10 +8912,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127362532</v>
+        <v>127363816</v>
       </c>
       <c r="B75" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>474704</v>
+        <v>474651</v>
       </c>
       <c r="R75" t="n">
-        <v>6848745</v>
+        <v>6848722</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9026,7 +9026,7 @@
         <v>127362721</v>
       </c>
       <c r="B76" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9134,10 +9134,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127363816</v>
+        <v>127362532</v>
       </c>
       <c r="B77" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9173,10 +9173,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>474651</v>
+        <v>474704</v>
       </c>
       <c r="R77" t="n">
-        <v>6848722</v>
+        <v>6848745</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9248,7 +9248,7 @@
         <v>127362954</v>
       </c>
       <c r="B78" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>127363287</v>
       </c>
       <c r="B79" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>127362906</v>
       </c>
       <c r="B80" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>127363073</v>
       </c>
       <c r="B81" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>127362816</v>
       </c>
       <c r="B82" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>127363338</v>
       </c>
       <c r="B83" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>127402462</v>
       </c>
       <c r="B84" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -5268,7 +5268,7 @@
         <v>127362304</v>
       </c>
       <c r="B42" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>127362966</v>
       </c>
       <c r="B43" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>127362991</v>
       </c>
       <c r="B44" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>127362853</v>
       </c>
       <c r="B45" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>127362917</v>
       </c>
       <c r="B46" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127363562</v>
       </c>
       <c r="B47" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>127362771</v>
       </c>
       <c r="B48" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>127362641</v>
       </c>
       <c r="B49" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127402375</v>
+        <v>127363457</v>
       </c>
       <c r="B50" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6161,20 +6161,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474605</v>
+        <v>474724</v>
       </c>
       <c r="R50" t="n">
-        <v>6848875</v>
+        <v>6848681</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6198,12 +6202,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6218,22 +6232,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127363457</v>
+        <v>127402375</v>
       </c>
       <c r="B51" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6258,24 +6272,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474724</v>
+        <v>474605</v>
       </c>
       <c r="R51" t="n">
-        <v>6848681</v>
+        <v>6848875</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6299,22 +6309,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6329,12 +6329,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6344,7 +6344,7 @@
         <v>127362672</v>
       </c>
       <c r="B52" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>127386307</v>
       </c>
       <c r="B53" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>127363005</v>
       </c>
       <c r="B54" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6684,10 +6684,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127402796</v>
+        <v>127402478</v>
       </c>
       <c r="B55" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6695,21 +6695,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474724</v>
+        <v>474626</v>
       </c>
       <c r="R55" t="n">
-        <v>6848762</v>
+        <v>6848851</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6781,10 +6781,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127402478</v>
+        <v>127402796</v>
       </c>
       <c r="B56" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,21 +6792,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474626</v>
+        <v>474724</v>
       </c>
       <c r="R56" t="n">
-        <v>6848851</v>
+        <v>6848762</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6881,7 +6881,7 @@
         <v>127362687</v>
       </c>
       <c r="B57" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>127362535</v>
       </c>
       <c r="B58" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>127361760</v>
       </c>
       <c r="B59" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>127361676</v>
       </c>
       <c r="B60" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>127361806</v>
       </c>
       <c r="B61" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>127362598</v>
       </c>
       <c r="B62" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>127363240</v>
       </c>
       <c r="B63" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>127362191</v>
       </c>
       <c r="B64" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>127363437</v>
       </c>
       <c r="B65" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>127361703</v>
       </c>
       <c r="B66" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>127361820</v>
       </c>
       <c r="B67" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>127362891</v>
       </c>
       <c r="B68" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>127362521</v>
       </c>
       <c r="B69" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>127363059</v>
       </c>
       <c r="B70" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>127362960</v>
       </c>
       <c r="B71" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>127362832</v>
       </c>
       <c r="B72" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>127362075</v>
       </c>
       <c r="B73" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>127363018</v>
       </c>
       <c r="B74" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>127363816</v>
       </c>
       <c r="B75" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>127362721</v>
       </c>
       <c r="B76" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>127362532</v>
       </c>
       <c r="B77" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>127362954</v>
       </c>
       <c r="B78" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>127363287</v>
       </c>
       <c r="B79" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>127362906</v>
       </c>
       <c r="B80" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>127363073</v>
       </c>
       <c r="B81" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>127362816</v>
       </c>
       <c r="B82" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>127363338</v>
       </c>
       <c r="B83" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>127402462</v>
       </c>
       <c r="B84" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -5268,7 +5268,7 @@
         <v>127362304</v>
       </c>
       <c r="B42" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>127362966</v>
       </c>
       <c r="B43" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>127362991</v>
       </c>
       <c r="B44" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>127362853</v>
       </c>
       <c r="B45" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>127362917</v>
       </c>
       <c r="B46" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127363562</v>
       </c>
       <c r="B47" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>127362771</v>
       </c>
       <c r="B48" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>127362641</v>
       </c>
       <c r="B49" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127363457</v>
+        <v>127402375</v>
       </c>
       <c r="B50" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6161,24 +6161,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474724</v>
+        <v>474605</v>
       </c>
       <c r="R50" t="n">
-        <v>6848681</v>
+        <v>6848875</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6202,22 +6198,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6232,22 +6218,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127402375</v>
+        <v>127363457</v>
       </c>
       <c r="B51" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6272,20 +6258,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474605</v>
+        <v>474724</v>
       </c>
       <c r="R51" t="n">
-        <v>6848875</v>
+        <v>6848681</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6309,12 +6299,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6329,12 +6329,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6344,7 +6344,7 @@
         <v>127362672</v>
       </c>
       <c r="B52" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>127386307</v>
       </c>
       <c r="B53" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6563,62 +6563,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127363005</v>
+        <v>127402796</v>
       </c>
       <c r="B54" t="n">
-        <v>98467</v>
+        <v>79061</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474656</v>
+        <v>474724</v>
       </c>
       <c r="R54" t="n">
-        <v>6848946</v>
+        <v>6848762</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6642,22 +6628,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6672,12 +6648,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6781,48 +6757,62 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127402796</v>
+        <v>127363005</v>
       </c>
       <c r="B56" t="n">
-        <v>79061</v>
+        <v>98468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474724</v>
+        <v>474656</v>
       </c>
       <c r="R56" t="n">
-        <v>6848762</v>
+        <v>6848946</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6846,12 +6836,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,12 +6866,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6881,7 +6881,7 @@
         <v>127362687</v>
       </c>
       <c r="B57" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>127362535</v>
       </c>
       <c r="B58" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>127361806</v>
       </c>
       <c r="B61" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>127362598</v>
       </c>
       <c r="B62" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>127363240</v>
       </c>
       <c r="B63" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>127362191</v>
       </c>
       <c r="B64" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>127363437</v>
       </c>
       <c r="B65" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>127361820</v>
       </c>
       <c r="B67" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>127362891</v>
       </c>
       <c r="B68" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>127362521</v>
       </c>
       <c r="B69" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>127363059</v>
       </c>
       <c r="B70" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>127362960</v>
       </c>
       <c r="B71" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>127362832</v>
       </c>
       <c r="B72" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>127362075</v>
       </c>
       <c r="B73" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>127363018</v>
       </c>
       <c r="B74" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>127363816</v>
       </c>
       <c r="B75" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>127362721</v>
       </c>
       <c r="B76" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>127362532</v>
       </c>
       <c r="B77" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>127362954</v>
       </c>
       <c r="B78" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>127363287</v>
       </c>
       <c r="B79" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>127362906</v>
       </c>
       <c r="B80" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>127363073</v>
       </c>
       <c r="B81" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127362816</v>
+        <v>127402462</v>
       </c>
       <c r="B82" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9727,21 +9727,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>474739</v>
+        <v>474630</v>
       </c>
       <c r="R82" t="n">
-        <v>6848699</v>
+        <v>6848862</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9768,22 +9764,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9798,22 +9784,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127363338</v>
+        <v>127362816</v>
       </c>
       <c r="B83" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9840,12 +9826,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9854,10 +9835,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>474730</v>
+        <v>474739</v>
       </c>
       <c r="R83" t="n">
-        <v>6848680</v>
+        <v>6848699</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9889,7 +9870,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9899,7 +9880,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9919,17 +9900,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127402462</v>
+        <v>127363338</v>
       </c>
       <c r="B84" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9954,17 +9935,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>474630</v>
+        <v>474730</v>
       </c>
       <c r="R84" t="n">
-        <v>6848862</v>
+        <v>6848680</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9991,12 +9981,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10011,12 +10011,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -6563,48 +6563,62 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127402796</v>
+        <v>127363005</v>
       </c>
       <c r="B54" t="n">
-        <v>79061</v>
+        <v>98468</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474724</v>
+        <v>474656</v>
       </c>
       <c r="R54" t="n">
-        <v>6848762</v>
+        <v>6848946</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6628,12 +6642,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6648,22 +6672,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127402478</v>
+        <v>127402796</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6671,21 +6695,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6695,10 +6719,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474626</v>
+        <v>474724</v>
       </c>
       <c r="R55" t="n">
-        <v>6848851</v>
+        <v>6848762</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6757,62 +6781,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127363005</v>
+        <v>127402478</v>
       </c>
       <c r="B56" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474656</v>
+        <v>474626</v>
       </c>
       <c r="R56" t="n">
-        <v>6848946</v>
+        <v>6848851</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6836,22 +6846,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,57 +6866,62 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127362687</v>
+        <v>127361760</v>
       </c>
       <c r="B57" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474755</v>
+        <v>474655</v>
       </c>
       <c r="R57" t="n">
-        <v>6848852</v>
+        <v>6848869</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6948,7 +6953,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6958,7 +6963,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6985,7 +6990,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127362535</v>
+        <v>127362687</v>
       </c>
       <c r="B58" t="n">
         <v>98468</v>
@@ -7013,31 +7018,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474796</v>
+        <v>474755</v>
       </c>
       <c r="R58" t="n">
-        <v>6848733</v>
+        <v>6848852</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7069,7 +7060,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7079,7 +7070,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7106,38 +7097,47 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127361760</v>
+        <v>127362535</v>
       </c>
       <c r="B59" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474655</v>
+        <v>474796</v>
       </c>
       <c r="R59" t="n">
-        <v>6848869</v>
+        <v>6848733</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7663,48 +7663,57 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127362191</v>
+        <v>127363437</v>
       </c>
       <c r="B64" t="n">
-        <v>91350</v>
+        <v>98468</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474687</v>
+        <v>474725</v>
       </c>
       <c r="R64" t="n">
-        <v>6848753</v>
+        <v>6848676</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7733,7 +7742,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7743,7 +7752,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7758,69 +7767,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127363437</v>
+        <v>127362191</v>
       </c>
       <c r="B65" t="n">
-        <v>98468</v>
+        <v>91350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474725</v>
+        <v>474687</v>
       </c>
       <c r="R65" t="n">
-        <v>6848676</v>
+        <v>6848753</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7874,12 +7874,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -5265,10 +5265,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127362304</v>
+        <v>127362966</v>
       </c>
       <c r="B42" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5309,13 +5309,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474663</v>
+        <v>474752</v>
       </c>
       <c r="R42" t="n">
-        <v>6848747</v>
+        <v>6848680</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5342,9 +5342,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5359,22 +5369,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127362966</v>
+        <v>127362304</v>
       </c>
       <c r="B43" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5401,12 +5411,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5415,13 +5425,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474752</v>
+        <v>474663</v>
       </c>
       <c r="R43" t="n">
-        <v>6848680</v>
+        <v>6848747</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5448,19 +5458,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5475,12 +5475,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5490,7 +5490,7 @@
         <v>127362991</v>
       </c>
       <c r="B44" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>127362853</v>
       </c>
       <c r="B45" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>127362917</v>
       </c>
       <c r="B46" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127363562</v>
       </c>
       <c r="B47" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>127362771</v>
       </c>
       <c r="B48" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>127362641</v>
       </c>
       <c r="B49" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127402375</v>
+        <v>127363457</v>
       </c>
       <c r="B50" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6161,20 +6161,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474605</v>
+        <v>474724</v>
       </c>
       <c r="R50" t="n">
-        <v>6848875</v>
+        <v>6848681</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6198,12 +6202,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6218,22 +6232,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127363457</v>
+        <v>127402375</v>
       </c>
       <c r="B51" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6258,24 +6272,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474724</v>
+        <v>474605</v>
       </c>
       <c r="R51" t="n">
-        <v>6848681</v>
+        <v>6848875</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6299,22 +6309,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6329,22 +6329,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127362672</v>
+        <v>127386307</v>
       </c>
       <c r="B52" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6371,27 +6371,26 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kontoret, Kontoret, Hjd</t>
+          <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474728</v>
+        <v>474736</v>
       </c>
       <c r="R52" t="n">
-        <v>6848726</v>
+        <v>6848669</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6418,49 +6417,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127386307</v>
+        <v>127362672</v>
       </c>
       <c r="B53" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6487,26 +6477,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474736</v>
+        <v>474728</v>
       </c>
       <c r="R53" t="n">
-        <v>6848669</v>
+        <v>6848726</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,30 +6524,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
         <v>127363005</v>
       </c>
       <c r="B54" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6684,10 +6684,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127402796</v>
+        <v>127402478</v>
       </c>
       <c r="B55" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6695,21 +6695,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474724</v>
+        <v>474626</v>
       </c>
       <c r="R55" t="n">
-        <v>6848762</v>
+        <v>6848851</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6781,10 +6781,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127402478</v>
+        <v>127402796</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6792,21 +6792,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474626</v>
+        <v>474724</v>
       </c>
       <c r="R56" t="n">
-        <v>6848851</v>
+        <v>6848762</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6990,10 +6990,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127362687</v>
+        <v>127362535</v>
       </c>
       <c r="B58" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7018,17 +7018,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474755</v>
+        <v>474796</v>
       </c>
       <c r="R58" t="n">
-        <v>6848852</v>
+        <v>6848733</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7060,7 +7074,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7070,7 +7084,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7097,10 +7111,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127362535</v>
+        <v>127362687</v>
       </c>
       <c r="B59" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7125,31 +7139,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474796</v>
+        <v>474755</v>
       </c>
       <c r="R59" t="n">
-        <v>6848733</v>
+        <v>6848852</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7218,48 +7218,57 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127361676</v>
+        <v>127361806</v>
       </c>
       <c r="B60" t="n">
-        <v>79061</v>
+        <v>98469</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474659</v>
+        <v>474668</v>
       </c>
       <c r="R60" t="n">
-        <v>6848942</v>
+        <v>6848864</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7288,7 +7297,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7298,7 +7307,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7313,22 +7322,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127361806</v>
+        <v>127362598</v>
       </c>
       <c r="B61" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7355,12 +7364,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7369,10 +7373,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474668</v>
+        <v>474703</v>
       </c>
       <c r="R61" t="n">
-        <v>6848864</v>
+        <v>6848747</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7404,7 +7408,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7414,7 +7418,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7441,52 +7445,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127362598</v>
+        <v>127361676</v>
       </c>
       <c r="B62" t="n">
-        <v>98468</v>
+        <v>79061</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>474703</v>
+        <v>474659</v>
       </c>
       <c r="R62" t="n">
-        <v>6848747</v>
+        <v>6848942</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7540,12 +7540,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7555,7 +7555,7 @@
         <v>127363240</v>
       </c>
       <c r="B63" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7663,57 +7663,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127363437</v>
+        <v>127362191</v>
       </c>
       <c r="B64" t="n">
-        <v>98468</v>
+        <v>91351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474725</v>
+        <v>474687</v>
       </c>
       <c r="R64" t="n">
-        <v>6848676</v>
+        <v>6848753</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7742,7 +7733,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7752,7 +7743,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7767,60 +7758,69 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127362191</v>
+        <v>127363437</v>
       </c>
       <c r="B65" t="n">
-        <v>91350</v>
+        <v>98469</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474687</v>
+        <v>474725</v>
       </c>
       <c r="R65" t="n">
-        <v>6848753</v>
+        <v>6848676</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7874,12 +7874,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8001,7 +8001,7 @@
         <v>127361820</v>
       </c>
       <c r="B67" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>127362891</v>
       </c>
       <c r="B68" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>127362521</v>
       </c>
       <c r="B69" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>127363059</v>
       </c>
       <c r="B70" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>127362960</v>
       </c>
       <c r="B71" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>127362832</v>
       </c>
       <c r="B72" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>127362075</v>
       </c>
       <c r="B73" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>127363018</v>
       </c>
       <c r="B74" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>127363816</v>
       </c>
       <c r="B75" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>127362721</v>
       </c>
       <c r="B76" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>127362532</v>
       </c>
       <c r="B77" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>127362954</v>
       </c>
       <c r="B78" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>127363287</v>
       </c>
       <c r="B79" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>127362906</v>
       </c>
       <c r="B80" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>127363073</v>
       </c>
       <c r="B81" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>127402462</v>
       </c>
       <c r="B82" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>127362816</v>
       </c>
       <c r="B83" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>127363338</v>
       </c>
       <c r="B84" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -5265,10 +5265,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127362966</v>
+        <v>127362304</v>
       </c>
       <c r="B42" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5309,13 +5309,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474752</v>
+        <v>474663</v>
       </c>
       <c r="R42" t="n">
-        <v>6848680</v>
+        <v>6848747</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5342,19 +5342,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5369,22 +5359,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127362304</v>
+        <v>127362966</v>
       </c>
       <c r="B43" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5411,12 +5401,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5425,13 +5415,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474663</v>
+        <v>474752</v>
       </c>
       <c r="R43" t="n">
-        <v>6848747</v>
+        <v>6848680</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5458,9 +5448,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5475,12 +5475,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5490,7 +5490,7 @@
         <v>127362991</v>
       </c>
       <c r="B44" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>127362853</v>
       </c>
       <c r="B45" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>127362917</v>
       </c>
       <c r="B46" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>127363562</v>
       </c>
       <c r="B47" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>127362771</v>
       </c>
       <c r="B48" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>127362641</v>
       </c>
       <c r="B49" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127363457</v>
+        <v>127402375</v>
       </c>
       <c r="B50" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6161,24 +6161,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474724</v>
+        <v>474605</v>
       </c>
       <c r="R50" t="n">
-        <v>6848681</v>
+        <v>6848875</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6202,22 +6198,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6232,22 +6218,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127402375</v>
+        <v>127363457</v>
       </c>
       <c r="B51" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6272,20 +6258,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474605</v>
+        <v>474724</v>
       </c>
       <c r="R51" t="n">
-        <v>6848875</v>
+        <v>6848681</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6309,12 +6299,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6329,22 +6329,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127386307</v>
+        <v>127362672</v>
       </c>
       <c r="B52" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6371,26 +6371,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474736</v>
+        <v>474728</v>
       </c>
       <c r="R52" t="n">
-        <v>6848669</v>
+        <v>6848726</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6417,40 +6418,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127362672</v>
+        <v>127386307</v>
       </c>
       <c r="B53" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6477,27 +6487,26 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kontoret, Kontoret, Hjd</t>
+          <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474728</v>
+        <v>474736</v>
       </c>
       <c r="R53" t="n">
-        <v>6848726</v>
+        <v>6848669</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6524,101 +6533,78 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127363005</v>
+        <v>127402796</v>
       </c>
       <c r="B54" t="n">
-        <v>98469</v>
+        <v>79061</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474656</v>
+        <v>474724</v>
       </c>
       <c r="R54" t="n">
-        <v>6848946</v>
+        <v>6848762</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6642,22 +6628,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6672,12 +6648,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6781,48 +6757,62 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127402796</v>
+        <v>127363005</v>
       </c>
       <c r="B56" t="n">
-        <v>79061</v>
+        <v>98470</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474724</v>
+        <v>474656</v>
       </c>
       <c r="R56" t="n">
-        <v>6848762</v>
+        <v>6848946</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6846,12 +6836,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,12 +6866,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127362535</v>
+        <v>127362687</v>
       </c>
       <c r="B58" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7018,31 +7018,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474796</v>
+        <v>474755</v>
       </c>
       <c r="R58" t="n">
-        <v>6848733</v>
+        <v>6848852</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7074,7 +7060,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7084,7 +7070,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7111,10 +7097,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127362687</v>
+        <v>127362535</v>
       </c>
       <c r="B59" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7139,17 +7125,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474755</v>
+        <v>474796</v>
       </c>
       <c r="R59" t="n">
-        <v>6848852</v>
+        <v>6848733</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7218,57 +7218,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127361806</v>
+        <v>127361676</v>
       </c>
       <c r="B60" t="n">
-        <v>98469</v>
+        <v>79061</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474668</v>
+        <v>474659</v>
       </c>
       <c r="R60" t="n">
-        <v>6848864</v>
+        <v>6848942</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7297,7 +7288,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7307,7 +7298,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7322,22 +7313,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127362598</v>
+        <v>127361806</v>
       </c>
       <c r="B61" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7364,7 +7355,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7373,10 +7369,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474703</v>
+        <v>474668</v>
       </c>
       <c r="R61" t="n">
-        <v>6848747</v>
+        <v>6848864</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7408,7 +7404,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7418,7 +7414,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7445,48 +7441,52 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127361676</v>
+        <v>127362598</v>
       </c>
       <c r="B62" t="n">
-        <v>79061</v>
+        <v>98470</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>474659</v>
+        <v>474703</v>
       </c>
       <c r="R62" t="n">
-        <v>6848942</v>
+        <v>6848747</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7540,12 +7540,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7555,7 +7555,7 @@
         <v>127363240</v>
       </c>
       <c r="B63" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>127362191</v>
       </c>
       <c r="B64" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>127363437</v>
       </c>
       <c r="B65" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7886,38 +7886,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127361703</v>
+        <v>127361820</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7926,13 +7925,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474655</v>
+        <v>474667</v>
       </c>
       <c r="R66" t="n">
-        <v>6848935</v>
+        <v>6848863</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7961,7 +7960,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7971,7 +7970,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7986,22 +7985,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127361820</v>
+        <v>127362891</v>
       </c>
       <c r="B67" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8028,7 +8027,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8037,10 +8041,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474667</v>
+        <v>474768</v>
       </c>
       <c r="R67" t="n">
-        <v>6848863</v>
+        <v>6848772</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8072,7 +8076,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8082,7 +8086,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8102,49 +8106,45 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127362891</v>
+        <v>127361703</v>
       </c>
       <c r="B68" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8153,13 +8153,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474768</v>
+        <v>474655</v>
       </c>
       <c r="R68" t="n">
-        <v>6848772</v>
+        <v>6848935</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8213,12 +8213,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8228,7 +8228,7 @@
         <v>127362521</v>
       </c>
       <c r="B69" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>127363059</v>
       </c>
       <c r="B70" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>127362960</v>
       </c>
       <c r="B71" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>127362832</v>
       </c>
       <c r="B72" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>127362075</v>
       </c>
       <c r="B73" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>127363018</v>
       </c>
       <c r="B74" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>127363816</v>
       </c>
       <c r="B75" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>127362721</v>
       </c>
       <c r="B76" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>127362532</v>
       </c>
       <c r="B77" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>127362954</v>
       </c>
       <c r="B78" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>127363287</v>
       </c>
       <c r="B79" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>127362906</v>
       </c>
       <c r="B80" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>127363073</v>
       </c>
       <c r="B81" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127402462</v>
+        <v>127362816</v>
       </c>
       <c r="B82" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9727,17 +9727,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>474630</v>
+        <v>474739</v>
       </c>
       <c r="R82" t="n">
-        <v>6848862</v>
+        <v>6848699</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9764,12 +9768,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9784,22 +9798,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127362816</v>
+        <v>127363338</v>
       </c>
       <c r="B83" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9826,7 +9840,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9835,10 +9854,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>474739</v>
+        <v>474730</v>
       </c>
       <c r="R83" t="n">
-        <v>6848699</v>
+        <v>6848680</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9870,7 +9889,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9880,7 +9899,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9900,17 +9919,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127363338</v>
+        <v>127402462</v>
       </c>
       <c r="B84" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9935,26 +9954,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>474730</v>
+        <v>474630</v>
       </c>
       <c r="R84" t="n">
-        <v>6848680</v>
+        <v>6848862</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9981,22 +9991,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10011,12 +10011,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -6133,7 +6133,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127402375</v>
+        <v>127363457</v>
       </c>
       <c r="B50" t="n">
         <v>98470</v>
@@ -6161,20 +6161,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474605</v>
+        <v>474724</v>
       </c>
       <c r="R50" t="n">
-        <v>6848875</v>
+        <v>6848681</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6198,12 +6202,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6218,19 +6232,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127363457</v>
+        <v>127402375</v>
       </c>
       <c r="B51" t="n">
         <v>98470</v>
@@ -6258,24 +6272,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474724</v>
+        <v>474605</v>
       </c>
       <c r="R51" t="n">
-        <v>6848681</v>
+        <v>6848875</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6299,22 +6309,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6329,12 +6329,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6563,48 +6563,62 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127402796</v>
+        <v>127363005</v>
       </c>
       <c r="B54" t="n">
-        <v>79061</v>
+        <v>98470</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474724</v>
+        <v>474656</v>
       </c>
       <c r="R54" t="n">
-        <v>6848762</v>
+        <v>6848946</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6628,12 +6642,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6648,22 +6672,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127402478</v>
+        <v>127402796</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6671,21 +6695,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6695,10 +6719,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474626</v>
+        <v>474724</v>
       </c>
       <c r="R55" t="n">
-        <v>6848851</v>
+        <v>6848762</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6757,62 +6781,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127363005</v>
+        <v>127402478</v>
       </c>
       <c r="B56" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474656</v>
+        <v>474626</v>
       </c>
       <c r="R56" t="n">
-        <v>6848946</v>
+        <v>6848851</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6836,22 +6846,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,12 +6866,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7663,48 +7663,57 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127362191</v>
+        <v>127363437</v>
       </c>
       <c r="B64" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474687</v>
+        <v>474725</v>
       </c>
       <c r="R64" t="n">
-        <v>6848753</v>
+        <v>6848676</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7733,7 +7742,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7743,7 +7752,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7758,69 +7767,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127363437</v>
+        <v>127362191</v>
       </c>
       <c r="B65" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474725</v>
+        <v>474687</v>
       </c>
       <c r="R65" t="n">
-        <v>6848676</v>
+        <v>6848753</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7874,49 +7874,50 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127361820</v>
+        <v>127361703</v>
       </c>
       <c r="B66" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7925,13 +7926,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474667</v>
+        <v>474655</v>
       </c>
       <c r="R66" t="n">
-        <v>6848863</v>
+        <v>6848935</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7960,7 +7961,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7970,7 +7971,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7985,19 +7986,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127362891</v>
+        <v>127361820</v>
       </c>
       <c r="B67" t="n">
         <v>98470</v>
@@ -8027,12 +8028,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8041,10 +8037,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474768</v>
+        <v>474667</v>
       </c>
       <c r="R67" t="n">
-        <v>6848772</v>
+        <v>6848863</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8076,7 +8072,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8086,7 +8082,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8106,45 +8102,49 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127361703</v>
+        <v>127362891</v>
       </c>
       <c r="B68" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8153,13 +8153,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474655</v>
+        <v>474768</v>
       </c>
       <c r="R68" t="n">
-        <v>6848935</v>
+        <v>6848772</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8213,12 +8213,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -9699,7 +9699,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127362816</v>
+        <v>127402462</v>
       </c>
       <c r="B82" t="n">
         <v>98470</v>
@@ -9727,21 +9727,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>474739</v>
+        <v>474630</v>
       </c>
       <c r="R82" t="n">
-        <v>6848699</v>
+        <v>6848862</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9768,22 +9764,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9798,19 +9784,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127363338</v>
+        <v>127362816</v>
       </c>
       <c r="B83" t="n">
         <v>98470</v>
@@ -9840,12 +9826,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9854,10 +9835,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>474730</v>
+        <v>474739</v>
       </c>
       <c r="R83" t="n">
-        <v>6848680</v>
+        <v>6848699</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9889,7 +9870,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9899,7 +9880,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9919,14 +9900,14 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127402462</v>
+        <v>127363338</v>
       </c>
       <c r="B84" t="n">
         <v>98470</v>
@@ -9954,17 +9935,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>474630</v>
+        <v>474730</v>
       </c>
       <c r="R84" t="n">
-        <v>6848862</v>
+        <v>6848680</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9991,12 +9981,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10011,12 +10011,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118668286</v>
+        <v>118668260</v>
       </c>
       <c r="B2" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474459</v>
+        <v>474477</v>
       </c>
       <c r="R2" t="n">
-        <v>6849011</v>
+        <v>6849113</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -761,18 +748,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,61 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118668288</v>
+        <v>127361676</v>
       </c>
       <c r="B3" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474489</v>
+        <v>474659</v>
       </c>
       <c r="R3" t="n">
-        <v>6849017</v>
+        <v>6848942</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,17 +841,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,38 +865,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118668308</v>
+        <v>127402796</v>
       </c>
       <c r="B4" t="n">
-        <v>78138</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,34 +894,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474281</v>
+        <v>474724</v>
       </c>
       <c r="R4" t="n">
-        <v>6849312</v>
+        <v>6848762</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,12 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,31 +968,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118668262</v>
+        <v>118668305</v>
       </c>
       <c r="B5" t="n">
-        <v>79111</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,21 +991,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1015,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474285</v>
+        <v>474253</v>
       </c>
       <c r="R5" t="n">
-        <v>6849320</v>
+        <v>6849332</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1127,15 +1081,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118668302</v>
+        <v>118668308</v>
       </c>
       <c r="B6" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1092,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474448</v>
+        <v>474281</v>
       </c>
       <c r="R6" t="n">
-        <v>6849112</v>
+        <v>6849312</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1233,61 +1182,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118668295</v>
+        <v>127362191</v>
       </c>
       <c r="B7" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474611</v>
+        <v>474687</v>
       </c>
       <c r="R7" t="n">
-        <v>6849103</v>
+        <v>6848753</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,17 +1247,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,76 +1271,66 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118668271</v>
+        <v>127362075</v>
       </c>
       <c r="B8" t="n">
-        <v>78229</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474250</v>
+        <v>474667</v>
       </c>
       <c r="R8" t="n">
-        <v>6849335</v>
+        <v>6848863</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1423,12 +1354,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,35 +1384,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118668303</v>
+        <v>118668302</v>
       </c>
       <c r="B9" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1499,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474498</v>
+        <v>474448</v>
       </c>
       <c r="R9" t="n">
-        <v>6849066</v>
+        <v>6849112</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1565,15 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118668273</v>
+        <v>118668303</v>
       </c>
       <c r="B10" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,42 +1508,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474331</v>
+        <v>474498</v>
       </c>
       <c r="R10" t="n">
-        <v>6849334</v>
+        <v>6849066</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1651,18 +1570,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1685,15 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118668298</v>
+        <v>118668304</v>
       </c>
       <c r="B11" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,42 +1609,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474502</v>
+        <v>474501</v>
       </c>
       <c r="R11" t="n">
-        <v>6849036</v>
+        <v>6849066</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1771,18 +1671,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1805,15 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118668285</v>
+        <v>127402478</v>
       </c>
       <c r="B12" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,42 +1710,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474508</v>
+        <v>474626</v>
       </c>
       <c r="R12" t="n">
-        <v>6849041</v>
+        <v>6848851</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1883,17 +1764,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,81 +1778,63 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118668279</v>
+        <v>118668271</v>
       </c>
       <c r="B13" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474461</v>
+        <v>474250</v>
       </c>
       <c r="R13" t="n">
-        <v>6849116</v>
+        <v>6849335</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2011,18 +1869,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2045,58 +1897,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118668282</v>
+        <v>118668261</v>
       </c>
       <c r="B14" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474482</v>
+        <v>474296</v>
       </c>
       <c r="R14" t="n">
-        <v>6849109</v>
+        <v>6849305</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2131,18 +1970,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2165,15 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118668261</v>
+        <v>118668262</v>
       </c>
       <c r="B15" t="n">
-        <v>79111</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474296</v>
+        <v>474285</v>
       </c>
       <c r="R15" t="n">
-        <v>6849305</v>
+        <v>6849320</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2271,58 +2099,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118668287</v>
+        <v>118668263</v>
       </c>
       <c r="B16" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474480</v>
+        <v>474253</v>
       </c>
       <c r="R16" t="n">
-        <v>6849016</v>
+        <v>6849332</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2357,18 +2172,12 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2391,61 +2200,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118668272</v>
+        <v>127361703</v>
       </c>
       <c r="B17" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474499</v>
+        <v>474655</v>
       </c>
       <c r="R17" t="n">
-        <v>6849218</v>
+        <v>6848935</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2469,17 +2270,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,38 +2294,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118668266</v>
+        <v>127361760</v>
       </c>
       <c r="B18" t="n">
-        <v>78230</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,37 +2323,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474350</v>
+        <v>474655</v>
       </c>
       <c r="R18" t="n">
-        <v>6849290</v>
+        <v>6848869</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2581,12 +2382,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,31 +2412,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118668277</v>
+        <v>118668272</v>
       </c>
       <c r="B19" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474434</v>
+        <v>474499</v>
       </c>
       <c r="R19" t="n">
-        <v>6849105</v>
+        <v>6849218</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2737,15 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118668278</v>
+        <v>118668273</v>
       </c>
       <c r="B20" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,10 +2582,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474442</v>
+        <v>474331</v>
       </c>
       <c r="R20" t="n">
-        <v>6849111</v>
+        <v>6849334</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2860,12 +2657,7 @@
         <v>118668276</v>
       </c>
       <c r="B21" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2977,15 +2769,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118668296</v>
+        <v>118668277</v>
       </c>
       <c r="B22" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3025,10 +2812,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474344</v>
+        <v>474434</v>
       </c>
       <c r="R22" t="n">
-        <v>6849284</v>
+        <v>6849105</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3065,7 +2852,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3097,15 +2884,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118668297</v>
+        <v>118668278</v>
       </c>
       <c r="B23" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3145,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474456</v>
+        <v>474442</v>
       </c>
       <c r="R23" t="n">
-        <v>6849018</v>
+        <v>6849111</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3185,7 +2967,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3217,15 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118668292</v>
+        <v>118668279</v>
       </c>
       <c r="B24" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474404</v>
+        <v>474461</v>
       </c>
       <c r="R24" t="n">
-        <v>6849287</v>
+        <v>6849116</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3305,7 +3082,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>7 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3337,50 +3114,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118668269</v>
+        <v>118668280</v>
       </c>
       <c r="B25" t="n">
-        <v>78230</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474281</v>
+        <v>474488</v>
       </c>
       <c r="R25" t="n">
-        <v>6849315</v>
+        <v>6849095</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3415,12 +3195,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3443,50 +3229,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118668260</v>
+        <v>118668281</v>
       </c>
       <c r="B26" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474477</v>
+        <v>474579</v>
       </c>
       <c r="R26" t="n">
-        <v>6849113</v>
+        <v>6849141</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3521,12 +3310,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3549,15 +3344,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118668300</v>
+        <v>118668282</v>
       </c>
       <c r="B27" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3597,10 +3387,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474357</v>
+        <v>474482</v>
       </c>
       <c r="R27" t="n">
-        <v>6849288</v>
+        <v>6849109</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3637,7 +3427,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,50 +3459,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118668265</v>
+        <v>118668283</v>
       </c>
       <c r="B28" t="n">
-        <v>79082</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474281</v>
+        <v>474330</v>
       </c>
       <c r="R28" t="n">
-        <v>6849316</v>
+        <v>6849329</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3747,12 +3540,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3775,15 +3574,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118668293</v>
+        <v>118668284</v>
       </c>
       <c r="B29" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,10 +3617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474329</v>
+        <v>474602</v>
       </c>
       <c r="R29" t="n">
-        <v>6849322</v>
+        <v>6849096</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3863,7 +3657,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>5 blomtjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,50 +3689,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118668305</v>
+        <v>118668285</v>
       </c>
       <c r="B30" t="n">
-        <v>78138</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474253</v>
+        <v>474508</v>
       </c>
       <c r="R30" t="n">
-        <v>6849332</v>
+        <v>6849041</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3973,12 +3770,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4001,50 +3804,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118668267</v>
+        <v>118668286</v>
       </c>
       <c r="B31" t="n">
-        <v>78230</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474296</v>
+        <v>474459</v>
       </c>
       <c r="R31" t="n">
-        <v>6849305</v>
+        <v>6849011</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4079,12 +3885,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4107,15 +3919,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118668289</v>
+        <v>118668287</v>
       </c>
       <c r="B32" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474510</v>
+        <v>474480</v>
       </c>
       <c r="R32" t="n">
-        <v>6849050</v>
+        <v>6849016</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4227,50 +4034,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118668304</v>
+        <v>118668288</v>
       </c>
       <c r="B33" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474501</v>
+        <v>474489</v>
       </c>
       <c r="R33" t="n">
-        <v>6849066</v>
+        <v>6849017</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4305,12 +4115,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4333,15 +4149,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118668284</v>
+        <v>118668289</v>
       </c>
       <c r="B34" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4381,10 +4192,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474602</v>
+        <v>474510</v>
       </c>
       <c r="R34" t="n">
-        <v>6849096</v>
+        <v>6849050</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4453,15 +4264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118668294</v>
+        <v>118668290</v>
       </c>
       <c r="B35" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,10 +4307,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474399</v>
+        <v>474513</v>
       </c>
       <c r="R35" t="n">
-        <v>6849297</v>
+        <v>6849159</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4541,7 +4347,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>3 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4573,15 +4379,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118668280</v>
+        <v>118668291</v>
       </c>
       <c r="B36" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4621,10 +4422,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474488</v>
+        <v>474499</v>
       </c>
       <c r="R36" t="n">
-        <v>6849095</v>
+        <v>6849233</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4693,15 +4494,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118668291</v>
+        <v>118668292</v>
       </c>
       <c r="B37" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4741,10 +4537,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474499</v>
+        <v>474404</v>
       </c>
       <c r="R37" t="n">
-        <v>6849233</v>
+        <v>6849287</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4781,7 +4577,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>7 blomstjälkar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4813,15 +4609,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118668290</v>
+        <v>118668293</v>
       </c>
       <c r="B38" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4861,10 +4652,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474513</v>
+        <v>474329</v>
       </c>
       <c r="R38" t="n">
-        <v>6849159</v>
+        <v>6849322</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4901,7 +4692,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>5 blomtjälkar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4933,15 +4724,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118668301</v>
+        <v>118668294</v>
       </c>
       <c r="B39" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4967,16 +4753,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474347</v>
+        <v>474399</v>
       </c>
       <c r="R39" t="n">
-        <v>6849287</v>
+        <v>6849297</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5011,12 +4805,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5039,50 +4839,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118668263</v>
+        <v>118668295</v>
       </c>
       <c r="B40" t="n">
-        <v>79111</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474253</v>
+        <v>474611</v>
       </c>
       <c r="R40" t="n">
-        <v>6849332</v>
+        <v>6849103</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5117,12 +4920,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5145,15 +4954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118668283</v>
+        <v>118668296</v>
       </c>
       <c r="B41" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,10 +4997,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474330</v>
+        <v>474344</v>
       </c>
       <c r="R41" t="n">
-        <v>6849329</v>
+        <v>6849284</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5233,7 +5037,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5265,10 +5069,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127362304</v>
+        <v>118668297</v>
       </c>
       <c r="B42" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5293,29 +5097,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kontoret, Kontoret, Hjd</t>
+          <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474663</v>
+        <v>474456</v>
       </c>
       <c r="R42" t="n">
-        <v>6848747</v>
+        <v>6849018</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5339,12 +5142,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5353,28 +5161,33 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127362966</v>
+        <v>118668298</v>
       </c>
       <c r="B43" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5399,29 +5212,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kontoret, Kontoret, Hjd</t>
+          <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474752</v>
+        <v>474502</v>
       </c>
       <c r="R43" t="n">
-        <v>6848680</v>
+        <v>6849036</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5445,22 +5257,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5469,28 +5276,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127362991</v>
+        <v>118668299</v>
       </c>
       <c r="B44" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5515,29 +5327,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kontoret, Kontoret, Hjd</t>
+          <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474773</v>
+        <v>474453</v>
       </c>
       <c r="R44" t="n">
-        <v>6848689</v>
+        <v>6849245</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5561,17 +5372,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>1 blommande</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5580,28 +5391,33 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127362853</v>
+        <v>118668300</v>
       </c>
       <c r="B45" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5626,29 +5442,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kontoret, Kontoret, Hjd</t>
+          <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474748</v>
+        <v>474357</v>
       </c>
       <c r="R45" t="n">
-        <v>6848724</v>
+        <v>6849288</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5672,17 +5487,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>3 blommande</t>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5691,28 +5506,33 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127362917</v>
+        <v>118668301</v>
       </c>
       <c r="B46" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5737,29 +5557,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bergmyran, Bergmyran, Hjd</t>
+          <t>Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474781</v>
+        <v>474347</v>
       </c>
       <c r="R46" t="n">
-        <v>6848688</v>
+        <v>6849287</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5783,12 +5594,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5803,22 +5614,26 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127363562</v>
+        <v>127361806</v>
       </c>
       <c r="B47" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5845,12 +5660,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5859,13 +5674,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474691</v>
+        <v>474668</v>
       </c>
       <c r="R47" t="n">
-        <v>6848604</v>
+        <v>6848864</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5892,9 +5707,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5909,22 +5734,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127362771</v>
+        <v>127361820</v>
       </c>
       <c r="B48" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,12 +5776,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5965,13 +5785,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474749</v>
+        <v>474667</v>
       </c>
       <c r="R48" t="n">
-        <v>6848712</v>
+        <v>6848863</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5998,9 +5818,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6015,22 +5845,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127362641</v>
+        <v>127362099</v>
       </c>
       <c r="B49" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6057,7 +5887,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6071,10 +5901,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474710</v>
+        <v>474642</v>
       </c>
       <c r="R49" t="n">
-        <v>6848736</v>
+        <v>6848760</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6133,10 +5963,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127363457</v>
+        <v>127362304</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6163,7 +5993,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6172,13 +6007,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474724</v>
+        <v>474663</v>
       </c>
       <c r="R50" t="n">
-        <v>6848681</v>
+        <v>6848747</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6205,19 +6040,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6232,22 +6057,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127402375</v>
+        <v>127362521</v>
       </c>
       <c r="B51" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6272,20 +6097,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474605</v>
+        <v>474703</v>
       </c>
       <c r="R51" t="n">
-        <v>6848875</v>
+        <v>6848742</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6309,12 +6143,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6329,22 +6173,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127362672</v>
+        <v>127362528</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6371,7 +6215,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -6385,13 +6234,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474728</v>
+        <v>474796</v>
       </c>
       <c r="R52" t="n">
-        <v>6848726</v>
+        <v>6848733</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6420,7 +6269,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6430,7 +6279,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6445,22 +6294,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127386307</v>
+        <v>127362532</v>
       </c>
       <c r="B53" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6487,26 +6336,22 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kontoret, Hjd</t>
+          <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474736</v>
+        <v>474704</v>
       </c>
       <c r="R53" t="n">
-        <v>6848669</v>
+        <v>6848745</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6533,40 +6378,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127363005</v>
+        <v>127362598</v>
       </c>
       <c r="B54" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6596,29 +6450,19 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474656</v>
+        <v>474703</v>
       </c>
       <c r="R54" t="n">
-        <v>6848946</v>
+        <v>6848747</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6647,7 +6491,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6657,7 +6501,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6672,60 +6516,64 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127402796</v>
+        <v>127362632</v>
       </c>
       <c r="B55" t="n">
-        <v>79061</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474724</v>
+        <v>474698</v>
       </c>
       <c r="R55" t="n">
-        <v>6848762</v>
+        <v>6848720</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6749,12 +6597,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6769,60 +6627,69 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127402478</v>
+        <v>127362641</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474626</v>
+        <v>474710</v>
       </c>
       <c r="R56" t="n">
-        <v>6848851</v>
+        <v>6848736</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6846,12 +6713,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,50 +6733,49 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127361760</v>
+        <v>127362666</v>
       </c>
       <c r="B57" t="n">
-        <v>57672</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6918,13 +6784,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474655</v>
+        <v>474698</v>
       </c>
       <c r="R57" t="n">
-        <v>6848869</v>
+        <v>6848728</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6953,7 +6819,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6963,7 +6829,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6978,22 +6844,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127362687</v>
+        <v>127362672</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7018,20 +6884,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474755</v>
+        <v>474728</v>
       </c>
       <c r="R58" t="n">
-        <v>6848852</v>
+        <v>6848726</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7060,7 +6935,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7070,7 +6945,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7085,22 +6960,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127362535</v>
+        <v>127362687</v>
       </c>
       <c r="B59" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7125,31 +7000,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474796</v>
+        <v>474755</v>
       </c>
       <c r="R59" t="n">
-        <v>6848733</v>
+        <v>6848852</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7181,7 +7042,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7191,7 +7052,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7218,48 +7079,52 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127361676</v>
+        <v>127362721</v>
       </c>
       <c r="B60" t="n">
-        <v>79061</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474659</v>
+        <v>474740</v>
       </c>
       <c r="R60" t="n">
-        <v>6848942</v>
+        <v>6848725</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7288,7 +7153,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7298,7 +7163,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7313,22 +7178,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127361806</v>
+        <v>127362771</v>
       </c>
       <c r="B61" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7355,12 +7220,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7369,13 +7234,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474668</v>
+        <v>474749</v>
       </c>
       <c r="R61" t="n">
-        <v>6848864</v>
+        <v>6848712</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7402,19 +7267,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:49</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7429,22 +7284,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127362598</v>
+        <v>127362816</v>
       </c>
       <c r="B62" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7480,10 +7335,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>474703</v>
+        <v>474739</v>
       </c>
       <c r="R62" t="n">
-        <v>6848747</v>
+        <v>6848699</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7515,7 +7370,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7525,7 +7380,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7552,10 +7407,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127363240</v>
+        <v>127362832</v>
       </c>
       <c r="B63" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7582,7 +7437,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7591,10 +7451,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>474737</v>
+        <v>474744</v>
       </c>
       <c r="R63" t="n">
-        <v>6848663</v>
+        <v>6848705</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7626,7 +7486,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7636,7 +7496,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7656,17 +7516,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127363437</v>
+        <v>127362853</v>
       </c>
       <c r="B64" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7693,12 +7553,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7707,13 +7567,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474725</v>
+        <v>474748</v>
       </c>
       <c r="R64" t="n">
-        <v>6848676</v>
+        <v>6848724</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7740,19 +7600,14 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:46</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>10:46</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>3 blommande</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7767,60 +7622,69 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127362191</v>
+        <v>127362891</v>
       </c>
       <c r="B65" t="n">
-        <v>91352</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474687</v>
+        <v>474768</v>
       </c>
       <c r="R65" t="n">
-        <v>6848753</v>
+        <v>6848772</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7849,7 +7713,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7859,7 +7723,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7874,50 +7738,49 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127361703</v>
+        <v>127362906</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7926,13 +7789,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>474655</v>
+        <v>474761</v>
       </c>
       <c r="R66" t="n">
-        <v>6848935</v>
+        <v>6848715</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7961,7 +7824,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7971,7 +7834,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7986,22 +7849,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127361820</v>
+        <v>127362917</v>
       </c>
       <c r="B67" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8028,22 +7891,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kontoret, Kontoret, Hjd</t>
+          <t>Bergmyran, Bergmyran, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474667</v>
+        <v>474781</v>
       </c>
       <c r="R67" t="n">
-        <v>6848863</v>
+        <v>6848688</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8070,19 +7938,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8097,22 +7955,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127362891</v>
+        <v>127362954</v>
       </c>
       <c r="B68" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8139,7 +7997,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -8153,10 +8011,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>474768</v>
+        <v>474761</v>
       </c>
       <c r="R68" t="n">
-        <v>6848772</v>
+        <v>6848679</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8188,7 +8046,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8198,7 +8056,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8225,10 +8083,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127362521</v>
+        <v>127362960</v>
       </c>
       <c r="B69" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8255,7 +8113,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -8269,13 +8132,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>474703</v>
+        <v>474647</v>
       </c>
       <c r="R69" t="n">
-        <v>6848742</v>
+        <v>6848955</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8304,7 +8167,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8314,7 +8177,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8329,22 +8192,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127363059</v>
+        <v>127362966</v>
       </c>
       <c r="B70" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8371,7 +8234,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8380,10 +8248,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>474726</v>
+        <v>474752</v>
       </c>
       <c r="R70" t="n">
-        <v>6848721</v>
+        <v>6848680</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8415,7 +8283,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8425,7 +8293,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8452,10 +8320,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127362960</v>
+        <v>127362991</v>
       </c>
       <c r="B71" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8482,7 +8350,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8490,24 +8358,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>474647</v>
+        <v>474773</v>
       </c>
       <c r="R71" t="n">
-        <v>6848955</v>
+        <v>6848689</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8534,19 +8397,14 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:32</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>1 blommande</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8561,22 +8419,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127362832</v>
+        <v>127362997</v>
       </c>
       <c r="B72" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8601,29 +8459,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>474744</v>
+        <v>474656</v>
       </c>
       <c r="R72" t="n">
-        <v>6848705</v>
+        <v>6848946</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8652,7 +8501,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8662,7 +8511,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8677,57 +8526,66 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127362075</v>
+        <v>127363018</v>
       </c>
       <c r="B73" t="n">
-        <v>91317</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>474667</v>
+        <v>474754</v>
       </c>
       <c r="R73" t="n">
-        <v>6848863</v>
+        <v>6848679</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8759,7 +8617,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8769,7 +8627,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8789,17 +8647,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127363018</v>
+        <v>127363059</v>
       </c>
       <c r="B74" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8826,12 +8684,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8840,10 +8693,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>474754</v>
+        <v>474726</v>
       </c>
       <c r="R74" t="n">
-        <v>6848679</v>
+        <v>6848721</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8875,7 +8728,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8885,7 +8738,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8912,10 +8765,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127363816</v>
+        <v>127363073</v>
       </c>
       <c r="B75" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8942,7 +8795,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8951,10 +8809,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>474651</v>
+        <v>474727</v>
       </c>
       <c r="R75" t="n">
-        <v>6848722</v>
+        <v>6848702</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8986,7 +8844,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8996,7 +8854,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9023,10 +8881,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127362721</v>
+        <v>127363240</v>
       </c>
       <c r="B76" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9053,7 +8911,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9062,10 +8920,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>474740</v>
+        <v>474737</v>
       </c>
       <c r="R76" t="n">
-        <v>6848725</v>
+        <v>6848663</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9097,7 +8955,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9107,7 +8965,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9127,17 +8985,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127362532</v>
+        <v>127363287</v>
       </c>
       <c r="B77" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9164,7 +9022,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9173,10 +9031,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>474704</v>
+        <v>474728</v>
       </c>
       <c r="R77" t="n">
-        <v>6848745</v>
+        <v>6848674</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9208,7 +9066,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9218,7 +9076,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9238,17 +9096,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127362954</v>
+        <v>127363338</v>
       </c>
       <c r="B78" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9275,7 +9133,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -9289,10 +9147,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>474761</v>
+        <v>474730</v>
       </c>
       <c r="R78" t="n">
-        <v>6848679</v>
+        <v>6848680</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9324,7 +9182,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9334,7 +9192,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9361,10 +9219,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127363287</v>
+        <v>127363437</v>
       </c>
       <c r="B79" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9391,7 +9249,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9400,10 +9263,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>474728</v>
+        <v>474725</v>
       </c>
       <c r="R79" t="n">
-        <v>6848674</v>
+        <v>6848676</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9435,7 +9298,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9445,7 +9308,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9472,10 +9335,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127362906</v>
+        <v>127363455</v>
       </c>
       <c r="B80" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9502,19 +9365,24 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kontoret, Kontoret, Hjd</t>
+          <t>Gryssjöhållan, Gryssjöhållan, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>474761</v>
+        <v>474700</v>
       </c>
       <c r="R80" t="n">
-        <v>6848715</v>
+        <v>6848568</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9544,19 +9412,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9571,22 +9429,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127363073</v>
+        <v>127363457</v>
       </c>
       <c r="B81" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9613,12 +9471,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9627,10 +9480,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>474727</v>
+        <v>474724</v>
       </c>
       <c r="R81" t="n">
-        <v>6848702</v>
+        <v>6848681</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9662,7 +9515,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9672,7 +9525,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9699,10 +9552,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127402462</v>
+        <v>127363498</v>
       </c>
       <c r="B82" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9727,20 +9580,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kontoret, Kontoret, Hjd</t>
+          <t>Gryssjöhållan, Gryssjöhållan, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>474630</v>
+        <v>474682</v>
       </c>
       <c r="R82" t="n">
-        <v>6848862</v>
+        <v>6848559</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9764,12 +9626,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9784,22 +9646,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127362816</v>
+        <v>127363562</v>
       </c>
       <c r="B83" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9829,19 +9691,24 @@
           <t>10</t>
         </is>
       </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kontoret, Kontoret, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>474739</v>
+        <v>474691</v>
       </c>
       <c r="R83" t="n">
-        <v>6848699</v>
+        <v>6848604</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9868,19 +9735,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>10:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9895,22 +9752,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin, Tilde Carlinger, Erik Christiansson, Alice Helander, Malte Lindberg, Elias Blad, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Sofia Damne, Ivar Anderberg, Emilia Blixt, Elis Lewin, Tilde Carlinger, Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127363338</v>
+        <v>127363816</v>
       </c>
       <c r="B84" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9937,12 +9794,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9951,10 +9803,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>474730</v>
+        <v>474651</v>
       </c>
       <c r="R84" t="n">
-        <v>6848680</v>
+        <v>6848722</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9986,7 +9838,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9996,7 +9848,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10020,6 +9872,1010 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>127386307</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>474736</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6848669</v>
+      </c>
+      <c r="S85" t="n">
+        <v>4</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127402375</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>474605</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6848875</v>
+      </c>
+      <c r="S86" t="n">
+        <v>15</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127402462</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>474630</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6848862</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>127403415</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>474586</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6848917</v>
+      </c>
+      <c r="S88" t="n">
+        <v>15</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>127362152</v>
+      </c>
+      <c r="B89" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Kontoret, Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>474644</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6848763</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Karin Berg Andersson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Karin Berg Andersson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>127363391</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Gryssjöhållan, Gryssjöhållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>474706</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6848549</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Karin Berg Andersson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Karin Berg Andersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>118668266</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>474350</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6849290</v>
+      </c>
+      <c r="S91" t="n">
+        <v>15</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>118668267</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>474296</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6849305</v>
+      </c>
+      <c r="S92" t="n">
+        <v>15</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>118668269</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>474281</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6849315</v>
+      </c>
+      <c r="S93" t="n">
+        <v>15</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>118668265</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Kontoret, Hjd</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>474281</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6849316</v>
+      </c>
+      <c r="S94" t="n">
+        <v>15</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41555-2023 artfynd.xlsx
+++ b/artfynd/A 41555-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AZ94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668260</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668305</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668308</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668302</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668303</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668304</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127402478</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668271</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668261</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668262</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668263</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1894,6 +1954,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668272</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2009,6 +2074,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668273</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2124,6 +2194,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668276</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2239,6 +2314,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668277</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2354,6 +2434,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668278</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2469,6 +2554,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668279</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2584,6 +2674,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668280</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2699,6 +2794,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668281</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2814,6 +2914,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668282</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2929,6 +3034,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668283</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3044,6 +3154,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668284</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3159,6 +3274,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668285</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3274,6 +3394,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668286</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3389,6 +3514,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668287</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3504,6 +3634,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668288</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3619,6 +3754,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668289</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3734,6 +3874,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668290</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3849,6 +3994,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668291</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3964,6 +4114,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668292</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4079,6 +4234,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668293</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4194,6 +4354,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668294</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4309,6 +4474,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668295</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4424,6 +4594,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668296</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4539,6 +4714,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668297</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4654,6 +4834,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668298</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4769,6 +4954,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668299</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4884,6 +5074,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668300</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4985,6 +5180,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668301</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5091,6 +5291,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362099</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5188,6 +5393,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127402375</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5285,6 +5495,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127402462</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5382,6 +5597,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127403415</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5479,6 +5699,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362152</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5580,6 +5805,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668266</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5681,6 +5911,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668267</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5782,6 +6017,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668269</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5883,6 +6123,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118668265</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5990,6 +6235,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127361676</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6087,6 +6337,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127402796</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6194,6 +6449,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362191</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6301,6 +6561,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362075</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6413,6 +6678,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127361703</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6525,6 +6795,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127361760</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6641,6 +6916,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127361806</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6752,6 +7032,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127361820</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6858,6 +7143,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362304</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6974,6 +7264,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362521</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7095,6 +7390,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362528</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7206,6 +7506,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362532</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7317,6 +7622,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362598</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7428,6 +7738,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362632</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7534,6 +7849,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362641</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7645,6 +7965,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362666</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7761,6 +8086,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362672</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7868,6 +8198,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362687</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7979,6 +8314,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362721</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8085,6 +8425,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362771</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8196,6 +8541,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362816</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8312,6 +8662,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362832</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8423,6 +8778,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362853</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8539,6 +8899,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362891</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8650,6 +9015,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362906</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8756,6 +9126,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362917</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8872,6 +9247,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362954</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8993,6 +9373,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362960</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9109,6 +9494,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362966</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9220,6 +9610,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362991</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9327,6 +9722,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362997</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9443,6 +9843,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127363018</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9554,6 +9959,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127363059</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9670,6 +10080,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127363073</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9781,6 +10196,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127363240</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9892,6 +10312,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127363287</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10008,6 +10433,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127363338</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10124,6 +10554,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127363437</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10230,6 +10665,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127363455</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10341,6 +10781,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127363457</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10447,6 +10892,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127363498</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10553,6 +11003,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127363562</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10664,6 +11119,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127363816</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10770,6 +11230,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386307</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10876,8 +11341,108 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127363391</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>